--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P84"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
@@ -470,10 +470,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC-LOGIN-001</v>
+        <v>TC-AQ-001</v>
       </c>
       <c r="B2" t="str">
-        <v>TC-LOGIN-001 | Valid credentials redirect to dashboard</v>
+        <v>TC-AQ-001 | Page loads with heading and pending items</v>
       </c>
       <c r="C2" t="str">
         <v>Login</v>
@@ -500,10 +500,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K2" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L2" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M2" t="str">
         <v>Playwright Automation</v>
@@ -520,10 +520,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC-LOGIN-002</v>
+        <v>TC-AQ-002</v>
       </c>
       <c r="B3" t="str">
-        <v>TC-LOGIN-002 | Login page loads with all required UI elements</v>
+        <v>TC-AQ-002 | Stat cards display all 4 metrics</v>
       </c>
       <c r="C3" t="str">
         <v>Login</v>
@@ -532,10 +532,10 @@
         <v>Positive</v>
       </c>
       <c r="E3" t="str">
-        <v>Critical</v>
+        <v>Low</v>
       </c>
       <c r="F3" t="str">
-        <v>Auto</v>
+        <v>API</v>
       </c>
       <c r="G3" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -550,10 +550,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K3" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L3" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M3" t="str">
         <v>Playwright Automation</v>
@@ -570,10 +570,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC-LOGIN-003</v>
+        <v>TC-AQ-003</v>
       </c>
       <c r="B4" t="str">
-        <v>TC-LOGIN-003 | Password field masked by default</v>
+        <v>TC-AQ-003 | Grid displays all 10 expected column headers</v>
       </c>
       <c r="C4" t="str">
         <v>Login</v>
@@ -585,7 +585,7 @@
         <v>Low</v>
       </c>
       <c r="F4" t="str">
-        <v>Unit</v>
+        <v>API</v>
       </c>
       <c r="G4" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -600,10 +600,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K4" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L4" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M4" t="str">
         <v>Playwright Automation</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC-LOGIN-004</v>
+        <v>TC-AQ-012</v>
       </c>
       <c r="B5" t="str">
-        <v>TC-LOGIN-004 | Password show/hide toggle changes input type</v>
+        <v>TC-AQ-012 | Search filters grid to matching rows</v>
       </c>
       <c r="C5" t="str">
         <v>Login</v>
@@ -635,7 +635,7 @@
         <v>Low</v>
       </c>
       <c r="F5" t="str">
-        <v>Unit</v>
+        <v>Auto</v>
       </c>
       <c r="G5" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -650,10 +650,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K5" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L5" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M5" t="str">
         <v>Playwright Automation</v>
@@ -670,19 +670,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC-LOGIN-005</v>
+        <v>TC-AQ-020</v>
       </c>
       <c r="B6" t="str">
-        <v>TC-LOGIN-005 | Remember Me checkbox toggles checked/unchecked</v>
+        <v>TC-AQ-020 | No-match search shows empty grid</v>
       </c>
       <c r="C6" t="str">
         <v>Login</v>
       </c>
       <c r="D6" t="str">
-        <v>Positive</v>
+        <v>Negative</v>
       </c>
       <c r="E6" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="F6" t="str">
         <v>Unit</v>
@@ -700,10 +700,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K6" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L6" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M6" t="str">
         <v>Playwright Automation</v>
@@ -720,22 +720,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC-LOGIN-006</v>
+        <v>TC-AQ-014</v>
       </c>
       <c r="B7" t="str">
-        <v>TC-LOGIN-006 | Invalid username + password shows error</v>
+        <v>TC-AQ-014 | EXPORT button is visible and clickable</v>
       </c>
       <c r="C7" t="str">
         <v>Login</v>
       </c>
       <c r="D7" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E7" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F7" t="str">
-        <v>API</v>
+        <v>Auto</v>
       </c>
       <c r="G7" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -750,10 +750,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K7" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L7" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M7" t="str">
         <v>Playwright Automation</v>
@@ -770,22 +770,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC-LOGIN-007</v>
+        <v>TC-AQ-015</v>
       </c>
       <c r="B8" t="str">
-        <v>TC-LOGIN-007 | Empty username + password — form blocked</v>
+        <v>TC-AQ-015 | Pagination shows correct format</v>
       </c>
       <c r="C8" t="str">
         <v>Login</v>
       </c>
       <c r="D8" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E8" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F8" t="str">
-        <v>Unit</v>
+        <v>API</v>
       </c>
       <c r="G8" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -800,10 +800,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K8" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L8" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M8" t="str">
         <v>Playwright Automation</v>
@@ -820,22 +820,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC-LOGIN-008</v>
+        <v>TC-AQ-019</v>
       </c>
       <c r="B9" t="str">
-        <v>TC-LOGIN-008 | Valid username + empty password — blocked</v>
+        <v>TC-AQ-019 | Unauthenticated user redirected to login</v>
       </c>
       <c r="C9" t="str">
         <v>Login</v>
       </c>
       <c r="D9" t="str">
-        <v>Negative</v>
+        <v>Security</v>
       </c>
       <c r="E9" t="str">
         <v>High</v>
       </c>
       <c r="F9" t="str">
-        <v>Unit</v>
+        <v>Auto</v>
       </c>
       <c r="G9" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -870,22 +870,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TC-LOGIN-009</v>
+        <v>TC-AQ-004</v>
       </c>
       <c r="B10" t="str">
-        <v>TC-LOGIN-009 | Empty username + valid password — blocked</v>
+        <v>TC-AQ-004 | Perform Action opens ActionQueueDetails page</v>
       </c>
       <c r="C10" t="str">
         <v>Login</v>
       </c>
       <c r="D10" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E10" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F10" t="str">
-        <v>Unit</v>
+        <v>API</v>
       </c>
       <c r="G10" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -900,10 +900,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K10" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L10" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M10" t="str">
         <v>Playwright Automation</v>
@@ -920,19 +920,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC-LOGIN-010</v>
+        <v>TC-AQ-005</v>
       </c>
       <c r="B11" t="str">
-        <v>TC-LOGIN-010 | Wrong username + correct password — rejected</v>
+        <v>TC-AQ-005 | Detail page displays all 5 information sections</v>
       </c>
       <c r="C11" t="str">
         <v>Login</v>
       </c>
       <c r="D11" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E11" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F11" t="str">
         <v>API</v>
@@ -950,10 +950,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K11" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L11" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M11" t="str">
         <v>Playwright Automation</v>
@@ -970,19 +970,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC-LOGIN-011</v>
+        <v>TC-AQ-018</v>
       </c>
       <c r="B12" t="str">
-        <v>TC-LOGIN-011 | Correct username + wrong password — rejected</v>
+        <v>TC-AQ-018 | Non-existent ticket ID handled gracefully</v>
       </c>
       <c r="C12" t="str">
         <v>Login</v>
       </c>
       <c r="D12" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E12" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F12" t="str">
         <v>API</v>
@@ -1000,10 +1000,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K12" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L12" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M12" t="str">
         <v>Playwright Automation</v>
@@ -1020,19 +1020,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TC-LOGIN-012</v>
+        <v>TC-AQ-026</v>
       </c>
       <c r="B13" t="str">
-        <v>TC-LOGIN-012 | 256-char username handled gracefully</v>
+        <v>TC-AQ-026 | TIMELINE button opens timeline view</v>
       </c>
       <c r="C13" t="str">
         <v>Login</v>
       </c>
       <c r="D13" t="str">
-        <v>Boundary</v>
+        <v>Positive</v>
       </c>
       <c r="E13" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F13" t="str">
         <v>API</v>
@@ -1050,10 +1050,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K13" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L13" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M13" t="str">
         <v>Playwright Automation</v>
@@ -1070,19 +1070,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TC-LOGIN-013</v>
+        <v>TC-AQ-006</v>
       </c>
       <c r="B14" t="str">
-        <v>TC-LOGIN-013 | 256-char password handled gracefully</v>
+        <v>TC-AQ-006 | APPROVE dialog opens with correct elements</v>
       </c>
       <c r="C14" t="str">
         <v>Login</v>
       </c>
       <c r="D14" t="str">
-        <v>Boundary</v>
+        <v>Positive</v>
       </c>
       <c r="E14" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F14" t="str">
         <v>API</v>
@@ -1100,10 +1100,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K14" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L14" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M14" t="str">
         <v>Playwright Automation</v>
@@ -1120,22 +1120,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC-LOGIN-014</v>
+        <v>TC-AQ-007</v>
       </c>
       <c r="B15" t="str">
-        <v>TC-LOGIN-014 | Whitespace-only username rejected</v>
+        <v>TC-AQ-007 | APPROVE with valid remarks submits successfully</v>
       </c>
       <c r="C15" t="str">
         <v>Login</v>
       </c>
       <c r="D15" t="str">
-        <v>Boundary</v>
+        <v>Positive</v>
       </c>
       <c r="E15" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F15" t="str">
-        <v>Unit</v>
+        <v>API</v>
       </c>
       <c r="G15" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -1150,10 +1150,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K15" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L15" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M15" t="str">
         <v>Playwright Automation</v>
@@ -1170,19 +1170,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC-LOGIN-015</v>
+        <v>TC-AQ-010</v>
       </c>
       <c r="B16" t="str">
-        <v>TC-LOGIN-015 | Special characters in username handled safely</v>
+        <v>TC-AQ-010 | Cancel APPROVE dismisses without submitting</v>
       </c>
       <c r="C16" t="str">
         <v>Login</v>
       </c>
       <c r="D16" t="str">
-        <v>Boundary</v>
+        <v>Positive</v>
       </c>
       <c r="E16" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F16" t="str">
         <v>API</v>
@@ -1200,10 +1200,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K16" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L16" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M16" t="str">
         <v>Playwright Automation</v>
@@ -1220,22 +1220,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC-LOGIN-016</v>
+        <v>TC-AQ-016</v>
       </c>
       <c r="B17" t="str">
-        <v>TC-LOGIN-016 | Username is case-insensitive (confirmed behaviour)</v>
+        <v>TC-AQ-016 | APPROVE empty remarks shows validation error</v>
       </c>
       <c r="C17" t="str">
         <v>Login</v>
       </c>
       <c r="D17" t="str">
-        <v>Boundary</v>
+        <v>Negative</v>
       </c>
       <c r="E17" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="F17" t="str">
-        <v>API</v>
+        <v>Unit</v>
       </c>
       <c r="G17" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -1250,10 +1250,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K17" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L17" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M17" t="str">
         <v>Playwright Automation</v>
@@ -1270,19 +1270,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC-LOGIN-017</v>
+        <v>TC-AQ-021</v>
       </c>
       <c r="B18" t="str">
-        <v>TC-LOGIN-017 | SQL injection in username handled safely</v>
+        <v>TC-AQ-021 | Single character remarks accepted</v>
       </c>
       <c r="C18" t="str">
         <v>Login</v>
       </c>
       <c r="D18" t="str">
-        <v>Security</v>
+        <v>Positive</v>
       </c>
       <c r="E18" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F18" t="str">
         <v>API</v>
@@ -1300,10 +1300,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K18" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L18" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M18" t="str">
         <v>Playwright Automation</v>
@@ -1320,19 +1320,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC-LOGIN-018</v>
+        <v>TC-AQ-022</v>
       </c>
       <c r="B19" t="str">
-        <v>TC-LOGIN-018 | SQL injection in password handled safely</v>
+        <v>TC-AQ-022 | Max length remarks (1000 chars) handled</v>
       </c>
       <c r="C19" t="str">
         <v>Login</v>
       </c>
       <c r="D19" t="str">
-        <v>Security</v>
+        <v>Boundary</v>
       </c>
       <c r="E19" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="F19" t="str">
         <v>API</v>
@@ -1350,10 +1350,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K19" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L19" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M19" t="str">
         <v>Playwright Automation</v>
@@ -1370,22 +1370,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TC-LOGIN-019</v>
+        <v>TC-AQ-023</v>
       </c>
       <c r="B20" t="str">
-        <v>TC-LOGIN-019 | XSS payload in username handled safely</v>
+        <v>TC-AQ-023 | Whitespace-only remarks rejected</v>
       </c>
       <c r="C20" t="str">
         <v>Login</v>
       </c>
       <c r="D20" t="str">
-        <v>Security</v>
+        <v>Boundary</v>
       </c>
       <c r="E20" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="F20" t="str">
-        <v>API</v>
+        <v>Unit</v>
       </c>
       <c r="G20" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
@@ -1400,10 +1400,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K20" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: url.includes is not a function</v>
       </c>
       <c r="L20" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M20" t="str">
         <v>Playwright Automation</v>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TC-LOGIN-020</v>
+        <v>TC-AQ-024</v>
       </c>
       <c r="B21" t="str">
-        <v>TC-LOGIN-020 | Unauthenticated access redirects to login</v>
+        <v>TC-AQ-024 | SQL injection in remarks is sanitized</v>
       </c>
       <c r="C21" t="str">
         <v>Login</v>
@@ -1435,49 +1435,3199 @@
         <v>High</v>
       </c>
       <c r="F21" t="str">
+        <v>API</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H21" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I21" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K21" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L21" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N21" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-AQ-025</v>
+      </c>
+      <c r="B22" t="str">
+        <v>TC-AQ-025 | XSS payload in remarks @security</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E22" t="str">
+        <v>High</v>
+      </c>
+      <c r="F22" t="str">
+        <v>API</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H22" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K22" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L22" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N22" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-AQ-008</v>
+      </c>
+      <c r="B23" t="str">
+        <v>TC-AQ-008 | REOPEN dialog opens with correct elements</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>API</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H23" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I23" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K23" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L23" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N23" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-AQ-009</v>
+      </c>
+      <c r="B24" t="str">
+        <v>TC-AQ-009 | REOPEN with valid remarks submits successfully</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>API</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H24" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I24" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K24" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L24" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N24" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-AQ-011</v>
+      </c>
+      <c r="B25" t="str">
+        <v>TC-AQ-011 | Cancel REOPEN dismisses without submitting</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>API</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H25" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K25" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L25" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N25" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-AQ-017</v>
+      </c>
+      <c r="B26" t="str">
+        <v>TC-AQ-017 | REOPEN empty remarks shows validation error</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E26" t="str">
+        <v>High</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H26" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I26" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K26" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L26" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N26" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC-AQ-013</v>
+      </c>
+      <c r="B27" t="str">
+        <v>TC-AQ-013 | BACK button navigates away from detail page</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
         <v>Auto</v>
       </c>
-      <c r="G21" t="str">
-        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
-      </c>
-      <c r="H21" t="str">
-        <v>(See Playwright spec: tests/login.spec.js)</v>
-      </c>
-      <c r="I21" t="str">
-        <v>See test-data/loginData.js</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Test assertions pass per spec definition</v>
-      </c>
-      <c r="K21" t="str">
+      <c r="G27" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H27" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I27" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K27" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="L27" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N27" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-TICKET-001</v>
+      </c>
+      <c r="B28" t="str">
+        <v>TC-TICKET-001 | Create Ticket page loads with all required fields</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H28" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I28" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K28" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L28" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N28" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-TICKET-002</v>
+      </c>
+      <c r="B29" t="str">
+        <v>TC-TICKET-002 | Project dropdown shows all available projects</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F29" t="str">
+        <v>API</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H29" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I29" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K29" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L29" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N29" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-TICKET-003</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TC-TICKET-003 | All 6 Ticket Type chips are visible</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H30" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I30" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K30" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L30" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N30" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-TICKET-004</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TC-TICKET-004 | All 6 platform chips visible on page load</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H31" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I31" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K31" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L31" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N31" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-TICKET-005</v>
+      </c>
+      <c r="B32" t="str">
+        <v>TC-TICKET-005 | Description character counter updates on input</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>API</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H32" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I32" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K32" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L32" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N32" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-TICKET-006</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TC-TICKET-006 | File attachment — PNG upload accepted</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>API</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H33" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K33" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L33" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N33" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-TICKET-007</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TC-TICKET-007 | Reset button clears all filled fields</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>API</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H34" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K34" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L34" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N34" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-TICKET-008</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TC-TICKET-008 | Submit with no fields filled shows Missing Information</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F35" t="str">
+        <v>API</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H35" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K35" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L35" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N35" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-TICKET-009</v>
+      </c>
+      <c r="B36" t="str">
+        <v>TC-TICKET-009 | Submit without Project shows validation error</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F36" t="str">
+        <v>API</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H36" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I36" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K36" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L36" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N36" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-TICKET-010</v>
+      </c>
+      <c r="B37" t="str">
+        <v>TC-TICKET-010 | Submit without Ticket Type shows validation error</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F37" t="str">
+        <v>API</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H37" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I37" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K37" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L37" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N37" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-TICKET-011</v>
+      </c>
+      <c r="B38" t="str">
+        <v>TC-TICKET-011 | Submit without Description shows validation error</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F38" t="str">
+        <v>API</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H38" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I38" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K38" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L38" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N38" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-TICKET-012</v>
+      </c>
+      <c r="B39" t="str">
+        <v>TC-TICKET-012 | Submit with description under 15 chars blocked</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>API</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H39" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I39" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K39" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L39" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N39" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-TICKET-013</v>
+      </c>
+      <c r="B40" t="str">
+        <v>TC-TICKET-013 | Page/Screen Name field is optional</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F40" t="str">
+        <v>API</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H40" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I40" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K40" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L40" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N40" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-TICKET-014</v>
+      </c>
+      <c r="B41" t="str">
+        <v>TC-TICKET-014 | Description with exactly 15 chars passes validation</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>API</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H41" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K41" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L41" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N41" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-TICKET-015</v>
+      </c>
+      <c r="B42" t="str">
+        <v>TC-TICKET-015 | Description at 2000 chars accepted by counter</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F42" t="str">
+        <v>API</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H42" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K42" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L42" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N42" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-TICKET-016</v>
+      </c>
+      <c r="B43" t="str">
+        <v>TC-TICKET-016 | Description over 2000 chars truncated to max</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F43" t="str">
+        <v>API</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H43" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K43" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L43" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N43" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-TICKET-017</v>
+      </c>
+      <c r="B44" t="str">
+        <v>TC-TICKET-017 | Long page name (300 chars) handled gracefully</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F44" t="str">
+        <v>API</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H44" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K44" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L44" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N44" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O44" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-TICKET-018</v>
+      </c>
+      <c r="B45" t="str">
+        <v>TC-TICKET-018 | Special characters in description handled safely</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F45" t="str">
+        <v>API</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H45" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I45" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K45" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L45" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N45" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O45" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-TICKET-019</v>
+      </c>
+      <c r="B46" t="str">
+        <v>TC-TICKET-019 | SQL injection in description handled safely</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E46" t="str">
+        <v>High</v>
+      </c>
+      <c r="F46" t="str">
+        <v>API</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H46" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I46" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K46" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L46" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N46" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O46" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-TICKET-020</v>
+      </c>
+      <c r="B47" t="str">
+        <v>TC-TICKET-020 | XSS payload in description handled safely</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E47" t="str">
+        <v>High</v>
+      </c>
+      <c r="F47" t="str">
+        <v>API</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H47" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I47" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K47" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L47" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N47" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O47" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-TICKET-021</v>
+      </c>
+      <c r="B48" t="str">
+        <v>TC-TICKET-021 | Unauthenticated access redirected to login</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E48" t="str">
+        <v>High</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H48" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I48" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K48" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L48" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N48" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O48" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-TICKET-022</v>
+      </c>
+      <c r="B49" t="str">
+        <v>TC-TICKET-022 | HTML injection in description handled safely</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F49" t="str">
+        <v>API</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H49" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I49" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K49" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="L49" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N49" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O49" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-DASH-001</v>
+      </c>
+      <c r="B50" t="str">
+        <v>TC-DASH-001 | Dashboard page loads with title and H1</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H50" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I50" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K50" t="str">
         <v>All assertions passed via Playwright</v>
       </c>
-      <c r="L21" t="str">
+      <c r="L50" t="str">
         <v>PASS</v>
       </c>
-      <c r="M21" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N21" t="str">
-        <v>29 Jun 2026</v>
-      </c>
-      <c r="O21" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
+      <c r="M50" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N50" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O50" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="B51" t="str">
+        <v>TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H51" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L51" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N51" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O51" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="B52" t="str">
+        <v>TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H52" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I52" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+      </c>
+      <c r="L52" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N52" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O52" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="B53" t="str">
+        <v>TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H53" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I53" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L53" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N53" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O53" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="B54" t="str">
+        <v>TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F54" t="str">
+        <v>API</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H54" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I54" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L54" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N54" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O54" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="B55" t="str">
+        <v>TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F55" t="str">
+        <v>API</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H55" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I55" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K55" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L55" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N55" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O55" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F56" t="str">
+        <v>API</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H56" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I56" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K56" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L56" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N56" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O56" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="B57" t="str">
+        <v>TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E57" t="str">
+        <v>High</v>
+      </c>
+      <c r="F57" t="str">
+        <v>API</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H57" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I57" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K57" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L57" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N57" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O57" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B58" t="str">
+        <v>TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H58" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I58" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K58" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N58" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O58" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TC-DASH-010</v>
+      </c>
+      <c r="B59" t="str">
+        <v>TC-DASH-010 | View All link navigates to ticket list</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H59" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I59" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K59" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N59" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O59" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="B60" t="str">
+        <v>TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F60" t="str">
+        <v>API</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H60" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I60" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 14 × locator resolved to &lt;a data-id="4" tab</v>
+      </c>
+      <c r="L60" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M60" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N60" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O60" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="B61" t="str">
+        <v>TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H61" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I61" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L61" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N61" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O61" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="B62" t="str">
+        <v>TC-DASH-013 | Search box accepts input</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H62" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I62" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K62" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N62" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O62" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TC-DASH-014</v>
+      </c>
+      <c r="B63" t="str">
+        <v>TC-DASH-014 | User profile dropdown shows username and links</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H63" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I63" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K63" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N63" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O63" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TC-DASH-015</v>
+      </c>
+      <c r="B64" t="str">
+        <v>TC-DASH-015 | Dashboard inaccessible without login</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H64" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I64" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K64" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N64" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O64" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B65" t="str">
+        <v>TC-LOGIN-001 | Valid credentials redirect to dashboard</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H65" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I65" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N65" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O65" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P65" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B66" t="str">
+        <v>TC-LOGIN-002 | Login page loads with all required UI elements</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H66" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I66" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N66" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O66" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P66" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B67" t="str">
+        <v>TC-LOGIN-003 | Password field masked by default</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H67" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I67" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N67" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O67" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P67" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TC-LOGIN-004</v>
+      </c>
+      <c r="B68" t="str">
+        <v>TC-LOGIN-004 | Password show/hide toggle changes input type</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H68" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I68" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N68" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O68" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P68" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TC-LOGIN-005</v>
+      </c>
+      <c r="B69" t="str">
+        <v>TC-LOGIN-005 | Remember Me checkbox toggles checked/unchecked</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H69" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I69" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N69" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O69" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P69" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TC-LOGIN-006</v>
+      </c>
+      <c r="B70" t="str">
+        <v>TC-LOGIN-006 | Invalid username + password shows error</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E70" t="str">
+        <v>High</v>
+      </c>
+      <c r="F70" t="str">
+        <v>API</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H70" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I70" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N70" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O70" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P70" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TC-LOGIN-007</v>
+      </c>
+      <c r="B71" t="str">
+        <v>TC-LOGIN-007 | Empty username + password — form blocked</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E71" t="str">
+        <v>High</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H71" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I71" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N71" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O71" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P71" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>TC-LOGIN-008</v>
+      </c>
+      <c r="B72" t="str">
+        <v>TC-LOGIN-008 | Valid username + empty password — blocked</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E72" t="str">
+        <v>High</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H72" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I72" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N72" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O72" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P72" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TC-LOGIN-009</v>
+      </c>
+      <c r="B73" t="str">
+        <v>TC-LOGIN-009 | Empty username + valid password — blocked</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E73" t="str">
+        <v>High</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H73" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I73" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N73" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O73" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P73" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>TC-LOGIN-010</v>
+      </c>
+      <c r="B74" t="str">
+        <v>TC-LOGIN-010 | Wrong username + correct password — rejected</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E74" t="str">
+        <v>High</v>
+      </c>
+      <c r="F74" t="str">
+        <v>API</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H74" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I74" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N74" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O74" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P74" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TC-LOGIN-011</v>
+      </c>
+      <c r="B75" t="str">
+        <v>TC-LOGIN-011 | Correct username + wrong password — rejected</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E75" t="str">
+        <v>High</v>
+      </c>
+      <c r="F75" t="str">
+        <v>API</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H75" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I75" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N75" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O75" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P75" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TC-LOGIN-012</v>
+      </c>
+      <c r="B76" t="str">
+        <v>TC-LOGIN-012 | 256-char username handled gracefully</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F76" t="str">
+        <v>API</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H76" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I76" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N76" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O76" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P76" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TC-LOGIN-013</v>
+      </c>
+      <c r="B77" t="str">
+        <v>TC-LOGIN-013 | 256-char password handled gracefully</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F77" t="str">
+        <v>API</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H77" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I77" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N77" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O77" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P77" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TC-LOGIN-014</v>
+      </c>
+      <c r="B78" t="str">
+        <v>TC-LOGIN-014 | Whitespace-only username rejected</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H78" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I78" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N78" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O78" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P78" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TC-LOGIN-015</v>
+      </c>
+      <c r="B79" t="str">
+        <v>TC-LOGIN-015 | Special characters in username handled safely</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F79" t="str">
+        <v>API</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H79" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I79" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N79" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O79" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P79" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TC-LOGIN-016</v>
+      </c>
+      <c r="B80" t="str">
+        <v>TC-LOGIN-016 | Username is case-insensitive (confirmed behaviour)</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F80" t="str">
+        <v>API</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H80" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I80" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N80" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O80" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P80" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TC-LOGIN-017</v>
+      </c>
+      <c r="B81" t="str">
+        <v>TC-LOGIN-017 | SQL injection in username handled safely</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E81" t="str">
+        <v>High</v>
+      </c>
+      <c r="F81" t="str">
+        <v>API</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H81" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I81" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N81" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O81" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P81" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TC-LOGIN-018</v>
+      </c>
+      <c r="B82" t="str">
+        <v>TC-LOGIN-018 | SQL injection in password handled safely</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E82" t="str">
+        <v>High</v>
+      </c>
+      <c r="F82" t="str">
+        <v>API</v>
+      </c>
+      <c r="G82" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H82" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I82" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N82" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O82" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P82" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TC-LOGIN-019</v>
+      </c>
+      <c r="B83" t="str">
+        <v>TC-LOGIN-019 | XSS payload in username handled safely</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E83" t="str">
+        <v>High</v>
+      </c>
+      <c r="F83" t="str">
+        <v>API</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H83" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I83" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N83" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O83" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P83" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TC-LOGIN-020</v>
+      </c>
+      <c r="B84" t="str">
+        <v>TC-LOGIN-020 | Unauthenticated access redirects to login</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E84" t="str">
+        <v>High</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H84" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I84" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Test passed via Playwright automation</v>
+      </c>
+      <c r="L84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N84" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="O84" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P84" t="str">
+        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P84"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P57"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1547,9 +4697,2865 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>BUG-LOGIN-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>[FAIL] TC-AQ-001 | Page loads with heading and pending items</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TC-AQ-001</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-001</v>
+      </c>
+      <c r="I2" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J2" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K2" t="str">
+        <v>New</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>BUG-LOGIN-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>[FAIL] TC-AQ-002 | Stat cards display all 4 metrics</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TC-AQ-002</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-002</v>
+      </c>
+      <c r="I3" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J3" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K3" t="str">
+        <v>New</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>BUG-LOGIN-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>[FAIL] TC-AQ-003 | Grid displays all 10 expected column headers</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TC-AQ-003</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-003</v>
+      </c>
+      <c r="I4" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J4" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K4" t="str">
+        <v>New</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M4" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>BUG-LOGIN-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>[FAIL] TC-AQ-012 | Search filters grid to matching rows</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D5" t="str">
+        <v>TC-AQ-012</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-012</v>
+      </c>
+      <c r="I5" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J5" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K5" t="str">
+        <v>New</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>BUG-LOGIN-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>[FAIL] TC-AQ-020 | No-match search shows empty grid</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D6" t="str">
+        <v>TC-AQ-020</v>
+      </c>
+      <c r="E6" t="str">
+        <v>High</v>
+      </c>
+      <c r="F6" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-020</v>
+      </c>
+      <c r="I6" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J6" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K6" t="str">
+        <v>New</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>BUG-LOGIN-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>[FAIL] TC-AQ-014 | EXPORT button is visible and clickable</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D7" t="str">
+        <v>TC-AQ-014</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-014</v>
+      </c>
+      <c r="I7" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J7" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K7" t="str">
+        <v>New</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M7" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>BUG-LOGIN-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>[FAIL] TC-AQ-015 | Pagination shows correct format</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TC-AQ-015</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-015</v>
+      </c>
+      <c r="I8" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J8" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K8" t="str">
+        <v>New</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M8" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>BUG-LOGIN-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>[FAIL] TC-AQ-004 | Perform Action opens ActionQueueDetails page</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TC-AQ-004</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-004</v>
+      </c>
+      <c r="I9" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J9" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K9" t="str">
+        <v>New</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M9" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>BUG-LOGIN-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>[FAIL] TC-AQ-005 | Detail page displays all 5 information sections</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D10" t="str">
+        <v>TC-AQ-005</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-005</v>
+      </c>
+      <c r="I10" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K10" t="str">
+        <v>New</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M10" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>BUG-LOGIN-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>[FAIL] TC-AQ-018 | Non-existent ticket ID handled gracefully</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D11" t="str">
+        <v>TC-AQ-018</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H11" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-018</v>
+      </c>
+      <c r="I11" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K11" t="str">
+        <v>New</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M11" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>BUG-LOGIN-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>[FAIL] TC-AQ-026 | TIMELINE button opens timeline view</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D12" t="str">
+        <v>TC-AQ-026</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F12" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-026</v>
+      </c>
+      <c r="I12" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J12" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K12" t="str">
+        <v>New</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M12" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>BUG-LOGIN-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>[FAIL] TC-AQ-006 | APPROVE dialog opens with correct elements</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D13" t="str">
+        <v>TC-AQ-006</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-006</v>
+      </c>
+      <c r="I13" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J13" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K13" t="str">
+        <v>New</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M13" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>BUG-LOGIN-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>[FAIL] TC-AQ-007 | APPROVE with valid remarks submits successfully</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D14" t="str">
+        <v>TC-AQ-007</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H14" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-007</v>
+      </c>
+      <c r="I14" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J14" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K14" t="str">
+        <v>New</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M14" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>BUG-LOGIN-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>[FAIL] TC-AQ-010 | Cancel APPROVE dismisses without submitting</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D15" t="str">
+        <v>TC-AQ-010</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H15" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-010</v>
+      </c>
+      <c r="I15" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J15" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K15" t="str">
+        <v>New</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M15" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>BUG-LOGIN-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>[FAIL] TC-AQ-016 | APPROVE empty remarks shows validation error</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D16" t="str">
+        <v>TC-AQ-016</v>
+      </c>
+      <c r="E16" t="str">
+        <v>High</v>
+      </c>
+      <c r="F16" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H16" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-016</v>
+      </c>
+      <c r="I16" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J16" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K16" t="str">
+        <v>New</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M16" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>BUG-LOGIN-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>[FAIL] TC-AQ-021 | Single character remarks accepted</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D17" t="str">
+        <v>TC-AQ-021</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F17" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H17" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-021</v>
+      </c>
+      <c r="I17" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J17" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K17" t="str">
+        <v>New</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M17" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>BUG-LOGIN-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>[FAIL] TC-AQ-022 | Max length remarks (1000 chars) handled</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D18" t="str">
+        <v>TC-AQ-022</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F18" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H18" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-022</v>
+      </c>
+      <c r="I18" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J18" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K18" t="str">
+        <v>New</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M18" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>BUG-LOGIN-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>[FAIL] TC-AQ-023 | Whitespace-only remarks rejected</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D19" t="str">
+        <v>TC-AQ-023</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F19" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H19" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-023</v>
+      </c>
+      <c r="I19" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J19" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K19" t="str">
+        <v>New</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M19" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>BUG-LOGIN-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>[FAIL] TC-AQ-024 | SQL injection in remarks is sanitized</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D20" t="str">
+        <v>TC-AQ-024</v>
+      </c>
+      <c r="E20" t="str">
+        <v>High</v>
+      </c>
+      <c r="F20" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H20" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-024</v>
+      </c>
+      <c r="I20" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J20" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K20" t="str">
+        <v>New</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M20" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>BUG-LOGIN-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>[FAIL] TC-AQ-025 | XSS payload in remarks @security</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D21" t="str">
+        <v>TC-AQ-025</v>
+      </c>
+      <c r="E21" t="str">
+        <v>High</v>
+      </c>
+      <c r="F21" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H21" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-025</v>
+      </c>
+      <c r="I21" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J21" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K21" t="str">
+        <v>New</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M21" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>BUG-LOGIN-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>[FAIL] TC-AQ-008 | REOPEN dialog opens with correct elements</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D22" t="str">
+        <v>TC-AQ-008</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F22" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-008</v>
+      </c>
+      <c r="I22" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J22" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K22" t="str">
+        <v>New</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M22" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>BUG-LOGIN-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>[FAIL] TC-AQ-009 | REOPEN with valid remarks submits successfully</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D23" t="str">
+        <v>TC-AQ-009</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H23" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-009</v>
+      </c>
+      <c r="I23" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J23" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K23" t="str">
+        <v>New</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M23" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>BUG-LOGIN-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>[FAIL] TC-AQ-011 | Cancel REOPEN dismisses without submitting</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D24" t="str">
+        <v>TC-AQ-011</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H24" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-011</v>
+      </c>
+      <c r="I24" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J24" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K24" t="str">
+        <v>New</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M24" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>BUG-LOGIN-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>[FAIL] TC-AQ-017 | REOPEN empty remarks shows validation error</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D25" t="str">
+        <v>TC-AQ-017</v>
+      </c>
+      <c r="E25" t="str">
+        <v>High</v>
+      </c>
+      <c r="F25" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H25" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-017</v>
+      </c>
+      <c r="I25" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J25" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K25" t="str">
+        <v>New</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M25" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>BUG-LOGIN-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>[FAIL] TC-AQ-013 | BACK button navigates away from detail page</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D26" t="str">
+        <v>TC-AQ-013</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F26" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H26" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-AQ-013</v>
+      </c>
+      <c r="I26" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J26" t="str">
+        <v>TypeError: url.includes is not a function</v>
+      </c>
+      <c r="K26" t="str">
+        <v>New</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M26" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>BUG-LOGIN-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>[FAIL] TC-TICKET-001 | Create Ticket page loads with all required fields</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D27" t="str">
+        <v>TC-TICKET-001</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F27" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H27" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-001</v>
+      </c>
+      <c r="I27" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J27" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K27" t="str">
+        <v>New</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M27" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>BUG-LOGIN-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>[FAIL] TC-TICKET-002 | Project dropdown shows all available projects</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D28" t="str">
+        <v>TC-TICKET-002</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H28" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-002</v>
+      </c>
+      <c r="I28" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J28" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K28" t="str">
+        <v>New</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M28" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>BUG-LOGIN-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>[FAIL] TC-TICKET-003 | All 6 Ticket Type chips are visible</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D29" t="str">
+        <v>TC-TICKET-003</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F29" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-003</v>
+      </c>
+      <c r="I29" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J29" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K29" t="str">
+        <v>New</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M29" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>BUG-LOGIN-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>[FAIL] TC-TICKET-004 | All 6 platform chips visible on page load</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D30" t="str">
+        <v>TC-TICKET-004</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F30" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-004</v>
+      </c>
+      <c r="I30" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J30" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K30" t="str">
+        <v>New</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M30" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>BUG-LOGIN-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>[FAIL] TC-TICKET-005 | Description character counter updates on input</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D31" t="str">
+        <v>TC-TICKET-005</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H31" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-005</v>
+      </c>
+      <c r="I31" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J31" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K31" t="str">
+        <v>New</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M31" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>BUG-LOGIN-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>[FAIL] TC-TICKET-006 | File attachment — PNG upload accepted</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D32" t="str">
+        <v>TC-TICKET-006</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H32" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-006</v>
+      </c>
+      <c r="I32" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J32" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K32" t="str">
+        <v>New</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M32" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>BUG-LOGIN-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>[FAIL] TC-TICKET-007 | Reset button clears all filled fields</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D33" t="str">
+        <v>TC-TICKET-007</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-007</v>
+      </c>
+      <c r="I33" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J33" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K33" t="str">
+        <v>New</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M33" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>BUG-LOGIN-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>[FAIL] TC-TICKET-008 | Submit with no fields filled shows Missing Information</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D34" t="str">
+        <v>TC-TICKET-008</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H34" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-008</v>
+      </c>
+      <c r="I34" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J34" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K34" t="str">
+        <v>New</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M34" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>BUG-LOGIN-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>[FAIL] TC-TICKET-009 | Submit without Project shows validation error</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D35" t="str">
+        <v>TC-TICKET-009</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F35" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H35" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-009</v>
+      </c>
+      <c r="I35" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J35" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K35" t="str">
+        <v>New</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M35" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>BUG-LOGIN-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>[FAIL] TC-TICKET-010 | Submit without Ticket Type shows validation error</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D36" t="str">
+        <v>TC-TICKET-010</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F36" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H36" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-010</v>
+      </c>
+      <c r="I36" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J36" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K36" t="str">
+        <v>New</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M36" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>BUG-LOGIN-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>[FAIL] TC-TICKET-011 | Submit without Description shows validation error</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D37" t="str">
+        <v>TC-TICKET-011</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F37" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-011</v>
+      </c>
+      <c r="I37" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J37" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K37" t="str">
+        <v>New</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M37" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>BUG-LOGIN-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>[FAIL] TC-TICKET-012 | Submit with description under 15 chars blocked</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D38" t="str">
+        <v>TC-TICKET-012</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F38" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H38" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-012</v>
+      </c>
+      <c r="I38" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J38" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K38" t="str">
+        <v>New</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M38" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>BUG-LOGIN-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>[FAIL] TC-TICKET-013 | Page/Screen Name field is optional</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D39" t="str">
+        <v>TC-TICKET-013</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H39" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-013</v>
+      </c>
+      <c r="I39" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J39" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K39" t="str">
+        <v>New</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M39" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>BUG-LOGIN-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>[FAIL] TC-TICKET-014 | Description with exactly 15 chars passes validation</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D40" t="str">
+        <v>TC-TICKET-014</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F40" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H40" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-014</v>
+      </c>
+      <c r="I40" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J40" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K40" t="str">
+        <v>New</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M40" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>BUG-LOGIN-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>[FAIL] TC-TICKET-015 | Description at 2000 chars accepted by counter</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D41" t="str">
+        <v>TC-TICKET-015</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H41" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-015</v>
+      </c>
+      <c r="I41" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J41" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K41" t="str">
+        <v>New</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M41" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>BUG-LOGIN-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>[FAIL] TC-TICKET-016 | Description over 2000 chars truncated to max</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D42" t="str">
+        <v>TC-TICKET-016</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F42" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H42" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-016</v>
+      </c>
+      <c r="I42" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J42" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K42" t="str">
+        <v>New</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M42" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>BUG-LOGIN-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>[FAIL] TC-TICKET-017 | Long page name (300 chars) handled gracefully</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D43" t="str">
+        <v>TC-TICKET-017</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F43" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-017</v>
+      </c>
+      <c r="I43" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J43" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K43" t="str">
+        <v>New</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M43" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>BUG-LOGIN-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>[FAIL] TC-TICKET-018 | Special characters in description handled safely</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D44" t="str">
+        <v>TC-TICKET-018</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F44" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G44" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H44" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-018</v>
+      </c>
+      <c r="I44" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J44" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K44" t="str">
+        <v>New</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M44" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>BUG-LOGIN-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>[FAIL] TC-TICKET-019 | SQL injection in description handled safely</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D45" t="str">
+        <v>TC-TICKET-019</v>
+      </c>
+      <c r="E45" t="str">
+        <v>High</v>
+      </c>
+      <c r="F45" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G45" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H45" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-019</v>
+      </c>
+      <c r="I45" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J45" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K45" t="str">
+        <v>New</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M45" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>BUG-LOGIN-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>[FAIL] TC-TICKET-020 | XSS payload in description handled safely</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D46" t="str">
+        <v>TC-TICKET-020</v>
+      </c>
+      <c r="E46" t="str">
+        <v>High</v>
+      </c>
+      <c r="F46" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G46" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H46" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-020</v>
+      </c>
+      <c r="I46" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J46" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K46" t="str">
+        <v>New</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M46" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>BUG-LOGIN-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>[FAIL] TC-TICKET-021 | Unauthenticated access redirected to login</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D47" t="str">
+        <v>TC-TICKET-021</v>
+      </c>
+      <c r="E47" t="str">
+        <v>High</v>
+      </c>
+      <c r="F47" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G47" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H47" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-021</v>
+      </c>
+      <c r="I47" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J47" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K47" t="str">
+        <v>New</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M47" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>BUG-LOGIN-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>[FAIL] TC-TICKET-022 | HTML injection in description handled safely</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D48" t="str">
+        <v>TC-TICKET-022</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F48" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G48" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H48" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-TICKET-022</v>
+      </c>
+      <c r="I48" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J48" t="str">
+        <v>TimeoutError: page.waitForSelector: Timeout 15000ms exceeded. Call log: - waiting for locator('#btnHeaderSubmit') to be visible</v>
+      </c>
+      <c r="K48" t="str">
+        <v>New</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M48" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>BUG-LOGIN-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D49" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F49" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G49" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H49" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-002</v>
+      </c>
+      <c r="I49" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K49" t="str">
+        <v>New</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M49" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>BUG-LOGIN-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>[FAIL] TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D50" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F50" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G50" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H50" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-003</v>
+      </c>
+      <c r="I50" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+      </c>
+      <c r="K50" t="str">
+        <v>New</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M50" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>BUG-LOGIN-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D51" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F51" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G51" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H51" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-004</v>
+      </c>
+      <c r="I51" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K51" t="str">
+        <v>New</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M51" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>BUG-LOGIN-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D52" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F52" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G52" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H52" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-005</v>
+      </c>
+      <c r="I52" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K52" t="str">
+        <v>New</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M52" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>BUG-LOGIN-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>[FAIL] TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D53" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F53" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G53" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H53" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-006</v>
+      </c>
+      <c r="I53" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J53" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K53" t="str">
+        <v>New</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M53" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>BUG-LOGIN-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D54" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F54" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G54" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H54" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-007</v>
+      </c>
+      <c r="I54" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J54" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K54" t="str">
+        <v>New</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M54" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>BUG-LOGIN-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>[FAIL] TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D55" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="E55" t="str">
+        <v>High</v>
+      </c>
+      <c r="F55" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G55" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H55" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-008</v>
+      </c>
+      <c r="I55" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J55" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K55" t="str">
+        <v>New</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M55" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>BUG-LOGIN-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D56" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F56" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G56" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H56" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-011</v>
+      </c>
+      <c r="I56" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 14 × locator resolved to &lt;a data-id="4" tab</v>
+      </c>
+      <c r="K56" t="str">
+        <v>New</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M56" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>BUG-LOGIN-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>[FAIL] TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D57" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F57" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G57" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H57" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/login.spec.js
+TC: TC-DASH-012</v>
+      </c>
+      <c r="I57" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K57" t="str">
+        <v>New</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M57" t="str">
+        <v>29 Jun 2026</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P57"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -509,13 +509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N2" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O2" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="3">
@@ -559,13 +559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N3" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O3" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="4">
@@ -609,13 +609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N4" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O4" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="5">
@@ -659,13 +659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N5" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O5" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="6">
@@ -709,13 +709,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N6" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O6" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="7">
@@ -759,13 +759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N7" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O7" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="8">
@@ -809,13 +809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N8" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O8" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="9">
@@ -850,7 +850,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K9" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L9" t="str">
         <v>PASS</v>
@@ -859,13 +859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N9" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O9" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="10">
@@ -909,13 +909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N10" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O10" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="11">
@@ -959,13 +959,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N11" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O11" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="12">
@@ -1009,13 +1009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N12" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O12" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="13">
@@ -1059,13 +1059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N13" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O13" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="14">
@@ -1109,13 +1109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N14" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O14" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="15">
@@ -1159,13 +1159,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N15" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O15" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="16">
@@ -1209,13 +1209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N16" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O16" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="17">
@@ -1259,13 +1259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N17" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O17" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="18">
@@ -1309,13 +1309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N18" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O18" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="19">
@@ -1359,13 +1359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N19" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O19" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="20">
@@ -1409,13 +1409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N20" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O20" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="21">
@@ -1459,13 +1459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N21" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O21" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="22">
@@ -1509,13 +1509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N22" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O22" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="23">
@@ -1559,13 +1559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N23" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O23" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="24">
@@ -1609,13 +1609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N24" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O24" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="25">
@@ -1659,13 +1659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N25" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O25" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="26">
@@ -1709,13 +1709,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N26" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O26" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="27">
@@ -1759,13 +1759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N27" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O27" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="28">
@@ -1809,13 +1809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N28" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O28" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="29">
@@ -1859,13 +1859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N29" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O29" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="30">
@@ -1909,13 +1909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N30" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O30" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="31">
@@ -1959,13 +1959,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N31" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O31" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="32">
@@ -2009,13 +2009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N32" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O32" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="33">
@@ -2059,13 +2059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N33" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O33" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="34">
@@ -2109,13 +2109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N34" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O34" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="35">
@@ -2159,13 +2159,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N35" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O35" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="36">
@@ -2209,13 +2209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N36" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O36" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="37">
@@ -2259,13 +2259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N37" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O37" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="38">
@@ -2309,13 +2309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N38" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O38" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="39">
@@ -2359,13 +2359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N39" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O39" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="40">
@@ -2409,13 +2409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N40" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O40" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="41">
@@ -2459,13 +2459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N41" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O41" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="42">
@@ -2509,13 +2509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N42" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O42" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="43">
@@ -2559,13 +2559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N43" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O43" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="44">
@@ -2609,13 +2609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N44" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O44" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="45">
@@ -2659,13 +2659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N45" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O45" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="46">
@@ -2709,13 +2709,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N46" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O46" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="47">
@@ -2759,13 +2759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N47" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O47" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P47" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="48">
@@ -2809,13 +2809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N48" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O48" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P48" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="49">
@@ -2859,13 +2859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N49" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O49" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P49" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="50">
@@ -2900,7 +2900,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K50" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L50" t="str">
         <v>PASS</v>
@@ -2909,13 +2909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N50" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O50" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="51">
@@ -2959,13 +2959,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N51" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O51" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="52">
@@ -3000,22 +3000,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K52" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L52" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M52" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N52" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O52" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="53">
@@ -3059,13 +3059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N53" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O53" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="54">
@@ -3109,13 +3109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N54" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O54" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="55">
@@ -3150,7 +3150,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K55" t="str">
-        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-01" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
       </c>
       <c r="L55" t="str">
         <v>FAIL</v>
@@ -3159,13 +3159,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N55" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O55" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="56">
@@ -3200,7 +3200,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K56" t="str">
-        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-01" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
       </c>
       <c r="L56" t="str">
         <v>FAIL</v>
@@ -3209,13 +3209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N56" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O56" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P56" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="57">
@@ -3250,7 +3250,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K57" t="str">
-        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-30" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-01" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
       </c>
       <c r="L57" t="str">
         <v>FAIL</v>
@@ -3259,13 +3259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N57" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O57" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P57" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="58">
@@ -3300,7 +3300,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K58" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L58" t="str">
         <v>PASS</v>
@@ -3309,13 +3309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N58" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O58" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P58" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="59">
@@ -3350,7 +3350,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K59" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L59" t="str">
         <v>PASS</v>
@@ -3359,13 +3359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N59" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O59" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P59" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="60">
@@ -3400,7 +3400,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K60" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 14 × locator resolved to &lt;a data-id="4" tab</v>
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 13 × locator resolved to &lt;a data-id="4" tab</v>
       </c>
       <c r="L60" t="str">
         <v>FAIL</v>
@@ -3409,13 +3409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N60" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O60" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P60" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="61">
@@ -3459,13 +3459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N61" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O61" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P61" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="62">
@@ -3500,7 +3500,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K62" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L62" t="str">
         <v>PASS</v>
@@ -3509,13 +3509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N62" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O62" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="63">
@@ -3550,7 +3550,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K63" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L63" t="str">
         <v>PASS</v>
@@ -3559,13 +3559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N63" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O63" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="64">
@@ -3600,7 +3600,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K64" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Test passed via Playwright automation</v>
       </c>
       <c r="L64" t="str">
         <v>PASS</v>
@@ -3609,13 +3609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N64" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O64" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P64" t="str">
-        <v/>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="65">
@@ -3659,13 +3659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N65" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O65" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P65" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="66">
@@ -3709,13 +3709,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N66" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O66" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P66" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="67">
@@ -3759,13 +3759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N67" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O67" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P67" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="68">
@@ -3809,13 +3809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N68" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O68" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P68" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="69">
@@ -3859,13 +3859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N69" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O69" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P69" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="70">
@@ -3909,13 +3909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N70" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O70" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P70" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="71">
@@ -3959,13 +3959,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N71" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O71" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P71" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="72">
@@ -4009,13 +4009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N72" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O72" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P72" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="73">
@@ -4059,13 +4059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N73" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O73" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P73" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="74">
@@ -4109,13 +4109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N74" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O74" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P74" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="75">
@@ -4159,13 +4159,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N75" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O75" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P75" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="76">
@@ -4209,13 +4209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N76" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O76" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P76" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="77">
@@ -4259,13 +4259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N77" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O77" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P77" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="78">
@@ -4309,13 +4309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N78" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O78" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P78" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="79">
@@ -4359,13 +4359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N79" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O79" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P79" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="80">
@@ -4409,13 +4409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N80" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O80" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P80" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="81">
@@ -4459,13 +4459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N81" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O81" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P81" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="82">
@@ -4509,13 +4509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N82" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O82" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P82" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="83">
@@ -4559,13 +4559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N83" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O83" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P83" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="84">
@@ -4609,13 +4609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N84" t="str">
-        <v>29 Jun 2026</v>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O84" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P84" t="str">
-        <v>Regression run — 6/29/2026, 8:17:28 PM</v>
+        <v>Regression run — 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
   </sheetData>
@@ -7178,7 +7178,7 @@
         <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
       </c>
       <c r="K50" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L50" t="str">
         <v>Playwright Automation</v>
@@ -7187,13 +7187,13 @@
         <v>29 Jun 2026</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>30 Jun 2026</v>
       </c>
       <c r="O50" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 6/30/2026, 8:17:22 PM</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">

--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -1440,10 +1440,10 @@
         <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
       </c>
       <c r="K19" t="str">
-        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L19" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M19" t="str">
         <v>Playwright Automation</v>
@@ -1647,58 +1647,6 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>BUG-LOGIN-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>SQL injection in password handled safely</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D2" t="str">
-        <v>TC-LOGIN-018</v>
-      </c>
-      <c r="E2" t="str">
-        <v>High</v>
-      </c>
-      <c r="F2" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G2" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Enter sajith_xyz + ' OR '1'='1 as password
-2. Click Sign In
-3. Check URL and auth state for SQL bypass</v>
-      </c>
-      <c r="I2" t="str">
-        <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
-      </c>
-      <c r="K2" t="str">
-        <v>New</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="M2" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P2"/>

--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -1440,10 +1440,10 @@
         <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
       </c>
       <c r="K19" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
       </c>
       <c r="L19" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M19" t="str">
         <v>Playwright Automation</v>
@@ -1647,6 +1647,58 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>BUG-LOGIN-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SQL injection in password handled safely</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TC-LOGIN-018</v>
+      </c>
+      <c r="E2" t="str">
+        <v>High</v>
+      </c>
+      <c r="F2" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter sajith_xyz + ' OR '1'='1 as password
+2. Click Sign In
+3. Check URL and auth state for SQL bypass</v>
+      </c>
+      <c r="I2" t="str">
+        <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
+      </c>
+      <c r="K2" t="str">
+        <v>New</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P2"/>

--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -1440,7 +1440,7 @@
         <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
       </c>
       <c r="K19" t="str">
-        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for" http://customerportal.dev-ts.online/Account/Login" navigation to finish...</v>
       </c>
       <c r="L19" t="str">
         <v>FAIL</v>
@@ -1678,7 +1678,7 @@
         <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
       </c>
       <c r="J2" t="str">
-        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for" http://customerportal.dev-ts.online/Account/Login" navigation to finish...</v>
       </c>
       <c r="K2" t="str">
         <v>New</v>

--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P101"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="46.83203125" customWidth="1"/>
@@ -468,12 +468,12 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>TC-LOGIN-001</v>
+        <v>TC-AQ-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Valid credentials redirect to dashboard</v>
+        <v>Page loads with heading and pending items</v>
       </c>
       <c r="C2" t="str">
         <v>Login</v>
@@ -488,9 +488,4009 @@
         <v>Auto</v>
       </c>
       <c r="G2" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H2" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('text=7 Pending Actions') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('text=7 Pending Actions')</v>
+      </c>
+      <c r="L2" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N2" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TC-AQ-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Stat cards display all 4 metrics</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>API</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H3" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K3" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N3" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TC-AQ-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Grid displays all 10 expected column headers</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>API</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H4" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I4" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K4" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N4" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TC-AQ-012</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Search filters grid to matching rows</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H5" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I5" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Error: expect(received).toBeGreaterThanOrEqual(expected) Expected: &gt;= 1 Received: 0</v>
+      </c>
+      <c r="L5" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N5" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TC-AQ-020</v>
+      </c>
+      <c r="B6" t="str">
+        <v>No-match search shows empty grid</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E6" t="str">
+        <v>High</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H6" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I6" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K6" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N6" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TC-AQ-014</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EXPORT button is visible and clickable</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H7" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I7" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K7" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N7" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TC-AQ-015</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Pagination shows correct format</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>API</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H8" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I8" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K8" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N8" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TC-AQ-019</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Unauthenticated user redirected to login</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E9" t="str">
+        <v>High</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H9" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I9" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K9" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N9" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TC-AQ-004</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Perform Action opens ActionQueueDetails page</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>API</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H10" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I10" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K10" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N10" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TC-AQ-005</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Detail page displays all 5 information sections</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>API</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H11" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I11" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K11" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N11" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TC-AQ-018</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Non-existent ticket ID handled gracefully</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F12" t="str">
+        <v>API</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H12" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I12" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K12" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N12" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TC-AQ-026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>TIMELINE button opens timeline view</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>API</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H13" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K13" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N13" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TC-AQ-006</v>
+      </c>
+      <c r="B14" t="str">
+        <v>APPROVE dialog opens with correct elements</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>API</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H14" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I14" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K14" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N14" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC-AQ-007</v>
+      </c>
+      <c r="B15" t="str">
+        <v>APPROVE with valid remarks submits successfully</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>API</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H15" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I15" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K15" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N15" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC-AQ-010</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Cancel APPROVE dismisses without submitting</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F16" t="str">
+        <v>API</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H16" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K16" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N16" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TC-AQ-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>APPROVE empty remarks shows validation error</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E17" t="str">
+        <v>High</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H17" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I17" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K17" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N17" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TC-AQ-021</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Single character remarks accepted</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>API</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H18" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I18" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L18" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N18" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TC-AQ-022</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Max length remarks (1000 chars) handled</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F19" t="str">
+        <v>API</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H19" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I19" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K19" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N19" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC-AQ-023</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Whitespace-only remarks rejected</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H20" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I20" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K20" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N20" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC-AQ-024</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SQL injection in remarks is sanitized</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E21" t="str">
+        <v>High</v>
+      </c>
+      <c r="F21" t="str">
+        <v>API</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H21" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I21" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K21" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N21" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-AQ-025</v>
+      </c>
+      <c r="B22" t="str">
+        <v>XSS payload in remarks @security</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E22" t="str">
+        <v>High</v>
+      </c>
+      <c r="F22" t="str">
+        <v>API</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H22" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K22" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N22" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-AQ-008</v>
+      </c>
+      <c r="B23" t="str">
+        <v>REOPEN dialog opens with correct elements</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>API</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H23" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I23" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K23" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N23" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-AQ-009</v>
+      </c>
+      <c r="B24" t="str">
+        <v>REOPEN with valid remarks submits successfully</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>API</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H24" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I24" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K24" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N24" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-AQ-011</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Cancel REOPEN dismisses without submitting</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>API</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H25" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K25" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N25" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-AQ-017</v>
+      </c>
+      <c r="B26" t="str">
+        <v>REOPEN empty remarks shows validation error</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E26" t="str">
+        <v>High</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H26" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I26" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K26" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N26" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC-AQ-013</v>
+      </c>
+      <c r="B27" t="str">
+        <v>BACK button navigates away from detail page</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H27" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I27" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Error: expect(received).not.toMatch(expected) Expected pattern: not /ActionQueueDetails/ Received string: "http://customerportal.dev-ts.online/Ticket/ActionQueueDetails/1345"</v>
+      </c>
+      <c r="L27" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N27" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-AU-007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Page loads with heading, stats, grid, Add New User button</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H28" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I28" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K28" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N28" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-AU-001</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Create Partner Admin — Automatic password</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F29" t="str">
+        <v>API</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H29" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I29" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="L29" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N29" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-AU-002</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Create Partner User — Automatic password</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>API</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H30" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I30" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="L30" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N30" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-AU-003</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Create user with Manual password</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>API</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H31" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I31" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="L31" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N31" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-AU-005</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Create user with Inactive status</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>API</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H32" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I32" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="L32" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N32" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-AU-008</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Cancel button closes modal without saving</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>API</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H33" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K33" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N33" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-AU-006</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Close (✕) button dismisses modal</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>API</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H34" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K34" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N34" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-AU-019</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Single character First Name (min boundary) accepted</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F35" t="str">
+        <v>API</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H35" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="L35" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N35" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-AU-013</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Empty form submit shows all validation errors</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E36" t="str">
+        <v>High</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H36" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I36" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K36" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N36" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-AU-010</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Empty First Name shows validation error</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E37" t="str">
+        <v>High</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H37" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I37" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K37" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N37" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-AU-017</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Invalid email format shows validation error</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E38" t="str">
+        <v>High</v>
+      </c>
+      <c r="F38" t="str">
+        <v>API</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H38" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I38" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K38" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N38" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-AU-018</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Partner User without customer shows validation error</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>API</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H39" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I39" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K39" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N39" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-AU-015</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Duplicate username — silent failure BUG-AU-001</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F40" t="str">
+        <v>API</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H40" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I40" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#wrapUsername .um-field-error') Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#wrapUsername .um-field-error') 14 × locator resolved to &lt;div class="um-field-e</v>
+      </c>
+      <c r="L40" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N40" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-AU-022</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Unauthenticated access redirects to login</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E41" t="str">
+        <v>High</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H41" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K41" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N41" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-AU-021</v>
+      </c>
+      <c r="B42" t="str">
+        <v>XSS payload in First Name does not execute</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E42" t="str">
+        <v>High</v>
+      </c>
+      <c r="F42" t="str">
+        <v>API</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H42" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K42" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N42" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-CT-001</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Submit valid ticket with all required fields</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F43" t="str">
+        <v>API</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H43" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K43" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N43" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-CT-002</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Submit valid ticket with optional Page/Screen Name</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F44" t="str">
+        <v>API</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H44" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K44" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N44" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O44" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-CT-003</v>
+      </c>
+      <c r="B45" t="str">
+        <v>All 6 ticket type chips are individually selectable</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H45" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I45" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K45" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N45" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O45" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-CT-004</v>
+      </c>
+      <c r="B46" t="str">
+        <v>All platform chips are individually selectable</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H46" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I46" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#platformChips .ct-type-chip').filter({ hasText: 'Backend' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#platformChips .ct-type-chip')</v>
+      </c>
+      <c r="L46" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N46" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O46" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-CT-005</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Reset button shows confirmation and clears all form fields</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F47" t="str">
+        <v>API</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H47" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I47" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K47" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N47" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O47" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-CT-006</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Character counter updates dynamically</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F48" t="str">
+        <v>API</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H48" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I48" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K48" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N48" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O48" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-CT-007</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Page loads with correct title, heading and all UI elements</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H49" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I49" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#descCount') Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#descCount') 14 × locator resolved to &lt;span id="descCount" class="ct-char"&gt;0 / 2000&lt;/span&gt; - unexp</v>
+      </c>
+      <c r="L49" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N49" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O49" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-CT-008</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Submit without project shows validation error</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F50" t="str">
+        <v>API</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H50" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I50" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K50" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#platformChips').locator('.ct-type-chip').filter({ hasText: 'Backend' }).first()</v>
+      </c>
+      <c r="L50" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N50" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O50" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-CT-009</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Submit without ticket type shows validation error</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F51" t="str">
+        <v>API</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H51" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K51" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N51" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O51" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-CT-010</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Submit without platform shows validation error</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F52" t="str">
+        <v>API</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H52" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I52" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K52" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N52" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O52" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-CT-011</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Submit without description shows validation error</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F53" t="str">
+        <v>API</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H53" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I53" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K53" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N53" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O53" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-CT-012</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Submit with description below 15 chars is rejected</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F54" t="str">
+        <v>API</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H54" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I54" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K54" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N54" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O54" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-CT-013</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Submit all fields empty shows all validation errors</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E55" t="str">
+        <v>High</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H55" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I55" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K55" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N55" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O55" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-CT-014</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Description exactly 15 chars (min boundary) is accepted</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F56" t="str">
+        <v>API</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H56" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I56" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K56" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N56" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O56" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC-CT-015</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Description exactly 14 chars (below min) is rejected</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F57" t="str">
+        <v>API</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H57" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I57" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K57" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N57" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O57" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC-CT-016</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Description exactly 2000 chars (max boundary) is accepted</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F58" t="str">
+        <v>API</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H58" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I58" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K58" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N58" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O58" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TC-CT-017</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Description 2001 chars should be blocked — BUG-CT-001</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F59" t="str">
+        <v>API</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H59" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I59" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K59" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N59" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O59" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TC-CT-018</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Page/Screen Name 300 chars handled gracefully</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F60" t="str">
+        <v>API</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H60" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I60" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K60" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M60" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N60" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O60" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TC-CT-019</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Unauthenticated access redirects to login</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E61" t="str">
+        <v>High</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H61" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I61" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K61" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N61" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O61" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TC-CT-020</v>
+      </c>
+      <c r="B62" t="str">
+        <v>SQL injection in description handled safely</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E62" t="str">
+        <v>High</v>
+      </c>
+      <c r="F62" t="str">
+        <v>API</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H62" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I62" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K62" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N62" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O62" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TC-CT-021</v>
+      </c>
+      <c r="B63" t="str">
+        <v>XSS payload in description does not execute</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E63" t="str">
+        <v>High</v>
+      </c>
+      <c r="F63" t="str">
+        <v>API</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H63" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I63" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K63" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N63" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O63" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TC-CT-022</v>
+      </c>
+      <c r="B64" t="str">
+        <v>HTML injection in description is sanitised</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F64" t="str">
+        <v>API</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H64" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I64" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K64" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N64" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O64" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TC-CT-023</v>
+      </c>
+      <c r="B65" t="str">
+        <v>XSS payload in Page/Screen Name does not execute</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E65" t="str">
+        <v>High</v>
+      </c>
+      <c r="F65" t="str">
+        <v>API</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H65" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I65" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K65" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N65" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O65" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC-CT-024</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Cancel Reset dialog retains all form fields</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F66" t="str">
+        <v>API</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H66" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I66" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K66" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('.swal2-actions button').nth(1) - locator resolved to &lt;button type="button" aria-label="" class="swal2-deny swal2-styled"&gt;No&lt;/button&gt; - attempting click action 2 × waiting for element to be visible, enabled and st</v>
+      </c>
+      <c r="L66" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N66" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O66" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TC-DASH-001</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Dashboard page loads with title and H1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H67" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I67" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K67" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N67" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O67" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="B68" t="str">
+        <v>All 4 stat cards visible with values</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H68" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I68" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L68" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N68" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O68" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="B69" t="str">
+        <v>OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H69" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I69" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K69" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N69" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O69" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H70" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I70" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L70" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N70" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O70" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F71" t="str">
+        <v>API</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H71" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I71" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L71" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N71" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O71" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Date range filter applies correctly</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F72" t="str">
+        <v>API</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H72" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I72" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K72" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-02" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L72" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N72" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O72" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Reset button clears date filter</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F73" t="str">
+        <v>API</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H73" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I73" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K73" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-02" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L73" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N73" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O73" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E74" t="str">
+        <v>High</v>
+      </c>
+      <c r="F74" t="str">
+        <v>API</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H74" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I74" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K74" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_apply') - locator resolved to &lt;button id="dr_apply" class="w-full text-[0.75rem] font-bold text-white bg-blue-600 hover:bg-blue-700 rounded py-1.5 transition-colors"&gt;Apply Range&lt;/button&gt; - attempting click ac</v>
+      </c>
+      <c r="L74" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N74" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O74" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Active Tickets table with correct columns</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H75" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I75" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K75" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N75" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O75" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TC-DASH-010</v>
+      </c>
+      <c r="B76" t="str">
+        <v>View All link navigates to ticket list</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H76" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I76" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K76" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N76" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O76" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="B77" t="str">
+        <v>All sidebar navigation links present</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F77" t="str">
+        <v>API</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H77" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I77" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 14 × locator resolved to &lt;a data-id="4" tab</v>
+      </c>
+      <c r="L77" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N77" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O77" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H78" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I78" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K78" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N78" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O78" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Search box accepts input</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H79" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I79" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K79" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N79" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O79" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TC-DASH-014</v>
+      </c>
+      <c r="B80" t="str">
+        <v>User profile dropdown shows username and links</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H80" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I80" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K80" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N80" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O80" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TC-DASH-015</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Dashboard inaccessible without login</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H81" t="str">
+        <v>(See Playwright spec: tests/login.spec.js)</v>
+      </c>
+      <c r="I81" t="str">
+        <v>See test-data/loginData.js</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K81" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N81" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O81" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Valid credentials redirect to dashboard</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G82" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H2" t="str" xml:space="preserve">
+      <c r="H82" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Clear all browser cookies
 2. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 3. Enter username: sajith_xyz
@@ -500,54 +4500,54 @@
 7. Verify URL = http://customerportal.dev-ts.online/
 8. Verify page title contains 'Dashboard'</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I82" t="str">
         <v>Username: sajith_xyz | Password: User@123</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J82" t="str">
         <v>User redirected to http://customerportal.dev-ts.online/; page title contains 'Dashboard'</v>
       </c>
-      <c r="K2" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N2" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O2" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
+      <c r="K82" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N82" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O82" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P82" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str">
         <v>TC-LOGIN-002</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B83" t="str">
         <v>Login page loads with all required UI elements</v>
       </c>
-      <c r="C3" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D3" t="str">
+      <c r="C83" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D83" t="str">
         <v>Positive</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E83" t="str">
         <v>Critical</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F83" t="str">
         <v>Auto</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G83" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
       </c>
-      <c r="H3" t="str" xml:space="preserve">
+      <c r="H83" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Verify page title = 'Sign In'
 3. Verify #UserName input is visible
@@ -555,107 +4555,107 @@
 5. Verify #RememberMe checkbox is visible
 6. Verify Sign In button is visible</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I83" t="str">
         <v>URL: http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J83" t="str">
         <v>Page title = 'Sign In'; all 4 elements visible: #UserName, #Password, #RememberMe, Sign In button</v>
       </c>
-      <c r="K3" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L3" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N3" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O3" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
+      <c r="K83" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N83" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O83" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P83" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str">
         <v>TC-LOGIN-003</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B84" t="str">
         <v>Password field masked by default</v>
       </c>
-      <c r="C4" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D4" t="str">
+      <c r="C84" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D84" t="str">
         <v>Positive</v>
       </c>
-      <c r="E4" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F4" t="str">
+      <c r="E84" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F84" t="str">
         <v>Unit</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G84" t="str">
         <v>Login page loaded in browser</v>
       </c>
-      <c r="H4" t="str" xml:space="preserve">
+      <c r="H84" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Locate the #Password input element
 3. Read the 'type' attribute on page load (before any user interaction)
 4. Verify type attribute = 'password'</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I84" t="str">
         <v>Element: #Password | Attribute inspected: type</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J84" t="str">
         <v>#Password input type = 'password' on initial page load; characters are masked</v>
       </c>
-      <c r="K4" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L4" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N4" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O4" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
+      <c r="K84" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N84" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O84" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P84" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85" t="str">
         <v>TC-LOGIN-004</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B85" t="str">
         <v>Password show/hide toggle changes input type</v>
       </c>
-      <c r="C5" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D5" t="str">
+      <c r="C85" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D85" t="str">
         <v>Positive</v>
       </c>
-      <c r="E5" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="E85" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F85" t="str">
         <v>Unit</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G85" t="str">
         <v>Login page loaded in browser</v>
       </c>
-      <c r="H5" t="str" xml:space="preserve">
+      <c r="H85" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Confirm #Password type = 'password' before interaction
 3. Click the eye icon toggle button (button[type="button"]:first)
@@ -663,107 +4663,107 @@
 5. Click the eye icon again
 6. Verify #Password type reverts to 'password'</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I85" t="str">
         <v>Toggle button: button[type="button"]:first-of-type (eye icon)</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J85" t="str">
         <v>Before click: type='password'; After click: type='text'; Toggle works bidirectionally</v>
       </c>
-      <c r="K5" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N5" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O5" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
+      <c r="K85" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N85" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O85" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P85" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
         <v>TC-LOGIN-005</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B86" t="str">
         <v>Remember Me checkbox toggles checked/unchecked</v>
       </c>
-      <c r="C6" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D6" t="str">
+      <c r="C86" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D86" t="str">
         <v>Positive</v>
       </c>
-      <c r="E6" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="E86" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F86" t="str">
         <v>Unit</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G86" t="str">
         <v>Login page loaded in browser</v>
       </c>
-      <c r="H6" t="str" xml:space="preserve">
+      <c r="H86" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Locate the #RememberMe checkbox
 3. Click to check — verify isChecked = true
 4. Click again to uncheck — verify isChecked = false</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I86" t="str">
         <v>Element: #RememberMe checkbox</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J86" t="str">
         <v>Checkbox toggles correctly: isChecked=true after check, isChecked=false after uncheck</v>
       </c>
-      <c r="K6" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M6" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N6" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O6" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str">
+      <c r="K86" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N86" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O86" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P86" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str">
         <v>TC-LOGIN-006</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B87" t="str">
         <v>Invalid username + password shows error</v>
       </c>
-      <c r="C7" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D7" t="str">
+      <c r="C87" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D87" t="str">
         <v>Negative</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E87" t="str">
         <v>High</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F87" t="str">
         <v>API</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G87" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H7" t="str" xml:space="preserve">
+      <c r="H87" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Clear all browser cookies
 2. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 3. Enter username: wrong_user
@@ -772,108 +4772,108 @@
 6. Verify page stays on /Account/Login
 7. Verify error message = 'Invalid user name or password'</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I87" t="str">
         <v>Username: wrong_user | Password: WrongPass@999</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J87" t="str">
         <v>Page stays on /Account/Login; error message 'Invalid user name or password' is displayed</v>
       </c>
-      <c r="K7" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N7" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O7" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8" t="str">
+      <c r="K87" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N87" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O87" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P87" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="88" xml:space="preserve">
+      <c r="A88" t="str">
         <v>TC-LOGIN-007</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B88" t="str">
         <v>Empty username + password — form blocked</v>
       </c>
-      <c r="C8" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D8" t="str">
+      <c r="C88" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D88" t="str">
         <v>Negative</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E88" t="str">
         <v>High</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F88" t="str">
         <v>Unit</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G88" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H8" t="str" xml:space="preserve">
+      <c r="H88" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Leave both username and password fields empty
 3. Click Sign In
 4. Verify URL remains on /Account/Login?ReturnUrl=%2F
 5. Verify form was not submitted</v>
       </c>
-      <c r="I8" t="str">
+      <c r="I88" t="str">
         <v>Username: (empty) | Password: (empty)</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J88" t="str">
         <v>Form not submitted; page stays on /Account/Login?ReturnUrl=%2F; browser validation blocks empty submission</v>
       </c>
-      <c r="K8" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L8" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N8" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O8" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
+      <c r="K88" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N88" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O88" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P88" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="89" xml:space="preserve">
+      <c r="A89" t="str">
         <v>TC-LOGIN-008</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B89" t="str">
         <v>Valid username + empty password — blocked</v>
       </c>
-      <c r="C9" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D9" t="str">
+      <c r="C89" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D89" t="str">
         <v>Negative</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E89" t="str">
         <v>High</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F89" t="str">
         <v>Unit</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G89" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H9" t="str" xml:space="preserve">
+      <c r="H89" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter username: sajith_xyz
 3. Leave password field empty
@@ -881,108 +4881,108 @@
 5. Verify page stays on /Account/Login?ReturnUrl=%2F
 6. Verify user is not authenticated</v>
       </c>
-      <c r="I9" t="str">
+      <c r="I89" t="str">
         <v>Username: sajith_xyz | Password: (empty)</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J89" t="str">
         <v>Login blocked; page stays on /Account/Login?ReturnUrl=%2F; user not authenticated</v>
       </c>
-      <c r="K9" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L9" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N9" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O9" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
+      <c r="K89" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N89" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O89" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P89" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90" t="str">
         <v>TC-LOGIN-009</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B90" t="str">
         <v>Empty username + valid password — blocked</v>
       </c>
-      <c r="C10" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D10" t="str">
+      <c r="C90" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D90" t="str">
         <v>Negative</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E90" t="str">
         <v>High</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F90" t="str">
         <v>Unit</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G90" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H10" t="str" xml:space="preserve">
+      <c r="H90" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Leave username field empty
 3. Enter password: User@123
 4. Click Sign In
 5. Verify page stays on /Account/Login?ReturnUrl=%2F</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I90" t="str">
         <v>Username: (empty) | Password: User@123</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J90" t="str">
         <v>Login blocked; page stays on /Account/Login?ReturnUrl=%2F; user not authenticated</v>
       </c>
-      <c r="K10" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L10" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N10" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O10" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str">
+      <c r="K90" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N90" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O90" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P90" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91" t="str">
         <v>TC-LOGIN-010</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B91" t="str">
         <v>Wrong username + correct password — rejected</v>
       </c>
-      <c r="C11" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D11" t="str">
+      <c r="C91" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D91" t="str">
         <v>Negative</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E91" t="str">
         <v>High</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F91" t="str">
         <v>API</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G91" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H11" t="str" xml:space="preserve">
+      <c r="H91" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter username: wrong_user
 3. Enter password: User@123 (valid password)
@@ -990,54 +4990,54 @@
 5. Verify page stays on /Account/Login
 6. Verify error message = 'Invalid user name or password'</v>
       </c>
-      <c r="I11" t="str">
+      <c r="I91" t="str">
         <v>Username: wrong_user | Password: User@123</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J91" t="str">
         <v>Login rejected; page stays on /Account/Login; error 'Invalid user name or password' shown</v>
       </c>
-      <c r="K11" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L11" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M11" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N11" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O11" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
+      <c r="K91" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N91" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O91" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P91" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str">
         <v>TC-LOGIN-011</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B92" t="str">
         <v>Correct username + wrong password — rejected</v>
       </c>
-      <c r="C12" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D12" t="str">
+      <c r="C92" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D92" t="str">
         <v>Negative</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E92" t="str">
         <v>High</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F92" t="str">
         <v>API</v>
       </c>
-      <c r="G12" t="str">
+      <c r="G92" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H12" t="str" xml:space="preserve">
+      <c r="H92" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter username: sajith_xyz (valid)
 3. Enter password: WrongPass@999 (wrong)
@@ -1045,54 +5045,54 @@
 5. Verify page stays on /Account/Login
 6. Verify error message = 'Invalid user name or password'</v>
       </c>
-      <c r="I12" t="str">
+      <c r="I92" t="str">
         <v>Username: sajith_xyz | Password: WrongPass@999</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J92" t="str">
         <v>Login rejected; page stays on /Account/Login; error 'Invalid user name or password' shown</v>
       </c>
-      <c r="K12" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L12" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M12" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N12" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O12" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str">
+      <c r="K92" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N92" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O92" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P92" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str">
         <v>TC-LOGIN-012</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B93" t="str">
         <v>256-char username handled gracefully</v>
       </c>
-      <c r="C13" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D13" t="str">
+      <c r="C93" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D93" t="str">
         <v>Boundary</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E93" t="str">
         <v>Medium</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F93" t="str">
         <v>API</v>
       </c>
-      <c r="G13" t="str">
+      <c r="G93" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H13" t="str" xml:space="preserve">
+      <c r="H93" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter 256-character string ('a'×256) into the username field
 3. Enter any value in the password field
@@ -1100,54 +5100,54 @@
 5. Verify page stays on /Account/Login (no redirect)
 6. Verify no HTTP 500 error and page title is not '500'</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I93" t="str">
         <v>Username: 'a'×256 (256 chars) | Password: anything</v>
       </c>
-      <c r="J13" t="str">
+      <c r="J93" t="str">
         <v>App handles oversized username gracefully; stays on /Account/Login; no 500 error or crash</v>
       </c>
-      <c r="K13" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L13" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N13" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O13" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
+      <c r="K93" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M93" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N93" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O93" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P93" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94" t="str">
         <v>TC-LOGIN-013</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B94" t="str">
         <v>256-char password handled gracefully</v>
       </c>
-      <c r="C14" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D14" t="str">
+      <c r="C94" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D94" t="str">
         <v>Boundary</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E94" t="str">
         <v>Medium</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F94" t="str">
         <v>API</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G94" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H14" t="str" xml:space="preserve">
+      <c r="H94" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter username: sajith_xyz
 3. Enter 256-character password ('P@ssword'+'x'×248) in password field
@@ -1155,54 +5155,54 @@
 5. Verify page stays on /Account/Login
 6. Verify no HTTP 500 error; page title does not contain '500'</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I94" t="str">
         <v>Username: sajith_xyz | Password: 'P@ssword'+'x'×248 (256 chars total)</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J94" t="str">
         <v>App handles oversized password gracefully; stays on /Account/Login; no 500 error or crash</v>
       </c>
-      <c r="K14" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L14" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M14" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N14" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O14" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str">
+      <c r="K94" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M94" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N94" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O94" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P94" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95" t="str">
         <v>TC-LOGIN-014</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B95" t="str">
         <v>Whitespace-only username rejected</v>
       </c>
-      <c r="C15" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D15" t="str">
+      <c r="C95" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D95" t="str">
         <v>Boundary</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E95" t="str">
         <v>Medium</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F95" t="str">
         <v>Unit</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G95" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H15" t="str" xml:space="preserve">
+      <c r="H95" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter '   ' (3 spaces) in the username field
 3. Enter password: User@123
@@ -1210,54 +5210,54 @@
 5. Verify user is not authenticated
 6. Verify page stays on /Account/Login?ReturnUrl=%2F</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I95" t="str">
         <v>Username: '   ' (3 spaces — whitespace only) | Password: User@123</v>
       </c>
-      <c r="J15" t="str">
+      <c r="J95" t="str">
         <v>Whitespace-only username not accepted; user not authenticated; stays on /Account/Login?ReturnUrl=%2F</v>
       </c>
-      <c r="K15" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L15" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M15" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N15" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O15" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
+      <c r="K95" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M95" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N95" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O95" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P95" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96" t="str">
         <v>TC-LOGIN-015</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B96" t="str">
         <v>Special characters in username handled safely</v>
       </c>
-      <c r="C16" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D16" t="str">
+      <c r="C96" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D96" t="str">
         <v>Boundary</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E96" t="str">
         <v>Medium</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F96" t="str">
         <v>API</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G96" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H16" t="str" xml:space="preserve">
+      <c r="H96" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter '!@#$%^&amp;*()' in the username field
 3. Enter password: User@123
@@ -1265,54 +5265,54 @@
 5. Verify page stays on /Account/Login
 6. Verify no HTTP 500 error or crash</v>
       </c>
-      <c r="I16" t="str">
+      <c r="I96" t="str">
         <v>Username: !@#$%^&amp;*() (special chars) | Password: User@123</v>
       </c>
-      <c r="J16" t="str">
+      <c r="J96" t="str">
         <v>Special characters handled safely; stays on /Account/Login; no 500 error; page title is 'Sign In'</v>
       </c>
-      <c r="K16" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L16" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M16" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N16" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O16" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
+      <c r="K96" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N96" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O96" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P96" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="97" xml:space="preserve">
+      <c r="A97" t="str">
         <v>TC-LOGIN-016</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B97" t="str">
         <v>Username is case-insensitive (confirmed behaviour)</v>
       </c>
-      <c r="C17" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D17" t="str">
+      <c r="C97" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D97" t="str">
         <v>Boundary</v>
       </c>
-      <c r="E17" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F17" t="str">
+      <c r="E97" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F97" t="str">
         <v>API</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G97" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H17" t="str" xml:space="preserve">
+      <c r="H97" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter username: SAJITH_XYZ (all uppercase)
 3. Enter password: User@123
@@ -1320,54 +5320,54 @@
 5. Observe result — does login succeed or fail?
 6. Document whether the app enforces username case sensitivity</v>
       </c>
-      <c r="I17" t="str">
+      <c r="I97" t="str">
         <v>Username: SAJITH_XYZ (all uppercase) | Password: User@123</v>
       </c>
-      <c r="J17" t="str">
+      <c r="J97" t="str">
         <v>Behaviour documented; app may or may not enforce case sensitivity; no crash expected</v>
       </c>
-      <c r="K17" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L17" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N17" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O17" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
+      <c r="K97" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M97" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N97" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O97" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P97" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98" t="str">
         <v>TC-LOGIN-017</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B98" t="str">
         <v>SQL injection in username handled safely</v>
       </c>
-      <c r="C18" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D18" t="str">
+      <c r="C98" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D98" t="str">
         <v>Security</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E98" t="str">
         <v>High</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F98" t="str">
         <v>API</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G98" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H18" t="str" xml:space="preserve">
+      <c r="H98" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter SQL injection payload in username: ' OR 1=1 --
 3. Enter any value in password field
@@ -1377,54 +5377,54 @@
 7. Verify no HTTP 500 SQL error is displayed
 8. Verify authentication was not bypassed</v>
       </c>
-      <c r="I18" t="str">
+      <c r="I98" t="str">
         <v>Username: ' OR 1=1 -- (SQL injection) | Password: anything</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J98" t="str">
         <v>SQL injection rejected; stays on /Account/Login; no SQL error exposed; authentication not bypassed</v>
       </c>
-      <c r="K18" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L18" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M18" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N18" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O18" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
+      <c r="K98" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N98" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O98" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P98" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str">
         <v>TC-LOGIN-018</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B99" t="str">
         <v>SQL injection in password handled safely</v>
       </c>
-      <c r="C19" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D19" t="str">
+      <c r="C99" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D99" t="str">
         <v>Security</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E99" t="str">
         <v>High</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F99" t="str">
         <v>API</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G99" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H19" t="str" xml:space="preserve">
+      <c r="H99" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter username: sajith_xyz
 3. Enter SQL injection payload in password: ' OR '1'='1
@@ -1433,54 +5433,54 @@
 6. Verify authentication was not bypassed
 7. Verify no SQL error is displayed</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I99" t="str">
         <v>Username: sajith_xyz | Password: ' OR '1'='1 (SQL injection)</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J99" t="str">
         <v>SQL injection in password rejected; authentication not bypassed; stays on /Account/Login; no SQL error</v>
       </c>
-      <c r="K19" t="str">
-        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for" http://customerportal.dev-ts.online/Account/Login" navigation to finish...</v>
-      </c>
-      <c r="L19" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="M19" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N19" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O19" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str">
+      <c r="K99" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M99" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N99" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O99" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P99" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" t="str">
         <v>TC-LOGIN-019</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B100" t="str">
         <v>XSS payload in username handled safely</v>
       </c>
-      <c r="C20" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D20" t="str">
+      <c r="C100" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D100" t="str">
         <v>Security</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E100" t="str">
         <v>High</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F100" t="str">
         <v>API</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G100" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online; sajith_xyz account active</v>
       </c>
-      <c r="H20" t="str" xml:space="preserve">
+      <c r="H100" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to http://customerportal.dev-ts.online/Account/Login?ReturnUrl=%2F
 2. Enter XSS payload in username: &lt;script&gt;alert('xss')&lt;/script&gt;
 3. Enter any value in password field
@@ -1489,95 +5489,95 @@
 6. Verify page stays on /Account/Login
 7. Verify no HTTP 500 error</v>
       </c>
-      <c r="I20" t="str">
+      <c r="I100" t="str">
         <v>Username: &lt;script&gt;alert('xss')&lt;/script&gt; | Password: anything</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J100" t="str">
         <v>XSS payload not executed; no JS alert fires; page stays on /Account/Login; input treated as plain text</v>
       </c>
-      <c r="K20" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L20" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M20" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N20" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O20" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
+      <c r="K100" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M100" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N100" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O100" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P100" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str">
         <v>TC-LOGIN-020</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B101" t="str">
         <v>Unauthenticated access redirects to login</v>
       </c>
-      <c r="C21" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D21" t="str">
+      <c r="C101" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D101" t="str">
         <v>Security</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E101" t="str">
         <v>High</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F101" t="str">
         <v>Auto</v>
       </c>
-      <c r="G21" t="str">
+      <c r="G101" t="str">
         <v>No active session (all cookies cleared)</v>
       </c>
-      <c r="H21" t="str" xml:space="preserve">
+      <c r="H101" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Clear all cookies using page.context().clearCookies()
 2. Navigate directly to http://customerportal.dev-ts.online/ (dashboard URL)
 3. Wait for navigation to complete
 4. Verify URL changes to /Account/Login?ReturnUrl=%2F
 5. Verify the login page is displayed (auth guard redirect active)</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I101" t="str">
         <v>Session: cleared | Direct target URL: http://customerportal.dev-ts.online/</v>
       </c>
-      <c r="J21" t="str">
+      <c r="J101" t="str">
         <v>Unauthenticated direct access blocked; redirected to /Account/Login?ReturnUrl=%2F; auth guard confirmed</v>
       </c>
-      <c r="K21" t="str">
-        <v>All assertions passed via Playwright</v>
-      </c>
-      <c r="L21" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="M21" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="N21" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="O21" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
+      <c r="K101" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M101" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N101" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O101" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P101" t="str">
+        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P101"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P23"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1681,27 +5681,1119 @@
         <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for" http://customerportal.dev-ts.online/Account/Login" navigation to finish...</v>
       </c>
       <c r="K2" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Fixed — verified in Playwright regression 7/1/2026, 8:22:09 PM</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>BUG-LOGIN-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Page loads with heading and pending items</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TC-AQ-001</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F3" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-001
+3. Observe failure</v>
+      </c>
+      <c r="I3" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('text=7 Pending Actions') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('text=7 Pending Actions')</v>
+      </c>
+      <c r="K3" t="str">
         <v>New</v>
       </c>
-      <c r="L2" t="str">
-        <v>Playwright Automation</v>
-      </c>
-      <c r="M2" t="str">
-        <v>01 Jul 2026</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="P2" t="str">
+      <c r="L3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>BUG-LOGIN-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Search filters grid to matching rows</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TC-AQ-012</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-012
+3. Observe failure</v>
+      </c>
+      <c r="I4" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Error: expect(received).toBeGreaterThanOrEqual(expected) Expected: &gt;= 1 Received: 0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>New</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M4" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>BUG-LOGIN-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Single character remarks accepted</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D5" t="str">
+        <v>TC-AQ-021</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-021
+3. Observe failure</v>
+      </c>
+      <c r="I5" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K5" t="str">
+        <v>New</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>BUG-LOGIN-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>BACK button navigates away from detail page</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D6" t="str">
+        <v>TC-AQ-013</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-013
+3. Observe failure</v>
+      </c>
+      <c r="I6" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Error: expect(received).not.toMatch(expected) Expected pattern: not /ActionQueueDetails/ Received string: "http://customerportal.dev-ts.online/Ticket/ActionQueueDetails/1345"</v>
+      </c>
+      <c r="K6" t="str">
+        <v>New</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>BUG-LOGIN-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Create Partner Admin — Automatic password</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D7" t="str">
+        <v>TC-AU-001</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F7" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AU-001
+3. Observe failure</v>
+      </c>
+      <c r="I7" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="K7" t="str">
+        <v>New</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M7" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>BUG-LOGIN-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Create Partner User — Automatic password</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TC-AU-002</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AU-002
+3. Observe failure</v>
+      </c>
+      <c r="I8" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="K8" t="str">
+        <v>New</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M8" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>BUG-LOGIN-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Create user with Manual password</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TC-AU-003</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AU-003
+3. Observe failure</v>
+      </c>
+      <c r="I9" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="K9" t="str">
+        <v>New</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M9" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>BUG-LOGIN-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Create user with Inactive status</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D10" t="str">
+        <v>TC-AU-005</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AU-005
+3. Observe failure</v>
+      </c>
+      <c r="I10" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="K10" t="str">
+        <v>New</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M10" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>BUG-LOGIN-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Single character First Name (min boundary) accepted</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D11" t="str">
+        <v>TC-AU-019</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F11" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AU-019
+3. Observe failure</v>
+      </c>
+      <c r="I11" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+      </c>
+      <c r="K11" t="str">
+        <v>New</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M11" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>BUG-LOGIN-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Duplicate username — silent failure BUG-AU-001</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D12" t="str">
+        <v>TC-AU-015</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F12" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AU-015
+3. Observe failure</v>
+      </c>
+      <c r="I12" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#wrapUsername .um-field-error') Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#wrapUsername .um-field-error') 14 × locator resolved to &lt;div class="um-field-e</v>
+      </c>
+      <c r="K12" t="str">
+        <v>New</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M12" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>BUG-LOGIN-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>All platform chips are individually selectable</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D13" t="str">
+        <v>TC-CT-004</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-CT-004
+3. Observe failure</v>
+      </c>
+      <c r="I13" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#platformChips .ct-type-chip').filter({ hasText: 'Backend' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#platformChips .ct-type-chip')</v>
+      </c>
+      <c r="K13" t="str">
+        <v>New</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M13" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>BUG-LOGIN-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Page loads with correct title, heading and all UI elements</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D14" t="str">
+        <v>TC-CT-007</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F14" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-CT-007
+3. Observe failure</v>
+      </c>
+      <c r="I14" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#descCount') Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#descCount') 14 × locator resolved to &lt;span id="descCount" class="ct-char"&gt;0 / 2000&lt;/span&gt; - unexp</v>
+      </c>
+      <c r="K14" t="str">
+        <v>New</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M14" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>BUG-LOGIN-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Submit without project shows validation error</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D15" t="str">
+        <v>TC-CT-008</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-CT-008
+3. Observe failure</v>
+      </c>
+      <c r="I15" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J15" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#platformChips').locator('.ct-type-chip').filter({ hasText: 'Backend' }).first()</v>
+      </c>
+      <c r="K15" t="str">
+        <v>New</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M15" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>BUG-LOGIN-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Cancel Reset dialog retains all form fields</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D16" t="str">
+        <v>TC-CT-024</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F16" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-CT-024
+3. Observe failure</v>
+      </c>
+      <c r="I16" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J16" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('.swal2-actions button').nth(1) - locator resolved to &lt;button type="button" aria-label="" class="swal2-deny swal2-styled"&gt;No&lt;/button&gt; - attempting click action 2 × waiting for element to be visible, enabled and st</v>
+      </c>
+      <c r="K16" t="str">
+        <v>New</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M16" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>BUG-LOGIN-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>All 4 stat cards visible with values</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D17" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F17" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-002
+3. Observe failure</v>
+      </c>
+      <c r="I17" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K17" t="str">
+        <v>New</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M17" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>BUG-LOGIN-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D18" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-004
+3. Observe failure</v>
+      </c>
+      <c r="I18" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K18" t="str">
+        <v>New</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M18" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>BUG-LOGIN-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D19" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F19" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-005
+3. Observe failure</v>
+      </c>
+      <c r="I19" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K19" t="str">
+        <v>New</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M19" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>BUG-LOGIN-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Date range filter applies correctly</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D20" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F20" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-006
+3. Observe failure</v>
+      </c>
+      <c r="I20" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J20" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-02" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K20" t="str">
+        <v>New</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M20" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>BUG-LOGIN-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Reset button clears date filter</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D21" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F21" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-007
+3. Observe failure</v>
+      </c>
+      <c r="I21" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J21" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-07-02" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K21" t="str">
+        <v>New</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M21" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>BUG-LOGIN-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D22" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="E22" t="str">
+        <v>High</v>
+      </c>
+      <c r="F22" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-008
+3. Observe failure</v>
+      </c>
+      <c r="I22" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J22" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_apply') - locator resolved to &lt;button id="dr_apply" class="w-full text-[0.75rem] font-bold text-white bg-blue-600 hover:bg-blue-700 rounded py-1.5 transition-colors"&gt;Apply Range&lt;/button&gt; - attempting click ac</v>
+      </c>
+      <c r="K22" t="str">
+        <v>New</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M22" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>BUG-LOGIN-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>All sidebar navigation links present</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D23" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-DASH-011
+3. Observe failure</v>
+      </c>
+      <c r="I23" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 14 × locator resolved to &lt;a data-id="4" tab</v>
+      </c>
+      <c r="K23" t="str">
+        <v>New</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M23" t="str">
+        <v>01 Jul 2026</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P23" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report_Git/Feature Reports/Login.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Login.xlsx
@@ -500,7 +500,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K2" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('text=7 Pending Actions') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('text=7 Pending Actions')</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L2" t="str">
         <v>FAIL</v>
@@ -509,13 +509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N2" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O2" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="3">
@@ -550,22 +550,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K3" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L3" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M3" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N3" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O3" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="4">
@@ -600,22 +600,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K4" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L4" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M4" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N4" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O4" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K5" t="str">
-        <v>Error: expect(received).toBeGreaterThanOrEqual(expected) Expected: &gt;= 1 Received: 0</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L5" t="str">
         <v>FAIL</v>
@@ -659,13 +659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N5" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O5" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="6">
@@ -700,22 +700,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K6" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L6" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M6" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N6" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O6" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="7">
@@ -750,22 +750,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K7" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L7" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M7" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N7" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O7" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="8">
@@ -800,22 +800,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K8" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L8" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M8" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N8" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O8" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="9">
@@ -859,13 +859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N9" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O9" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="10">
@@ -900,22 +900,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K10" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L10" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M10" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N10" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O10" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="11">
@@ -950,22 +950,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K11" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L11" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M11" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N11" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O11" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="12">
@@ -1009,13 +1009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N12" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O12" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="13">
@@ -1050,22 +1050,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K13" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L13" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M13" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N13" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O13" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="14">
@@ -1100,22 +1100,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K14" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L14" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M14" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N14" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O14" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="15">
@@ -1150,22 +1150,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K15" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L15" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M15" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N15" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O15" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="16">
@@ -1200,22 +1200,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K16" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L16" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M16" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N16" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O16" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="17">
@@ -1250,22 +1250,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K17" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L17" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M17" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N17" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O17" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="18">
@@ -1300,7 +1300,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K18" t="str">
-        <v>Error: expect(received).toBeTruthy() Received: false</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L18" t="str">
         <v>FAIL</v>
@@ -1309,13 +1309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N18" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O18" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="19">
@@ -1350,22 +1350,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K19" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L19" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M19" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N19" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O19" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="20">
@@ -1400,22 +1400,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K20" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L20" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M20" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N20" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O20" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="21">
@@ -1450,22 +1450,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K21" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L21" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M21" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N21" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O21" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="22">
@@ -1500,22 +1500,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K22" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L22" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M22" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N22" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O22" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="23">
@@ -1550,22 +1550,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K23" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L23" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M23" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N23" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O23" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="24">
@@ -1600,22 +1600,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K24" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L24" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M24" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N24" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O24" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="25">
@@ -1650,22 +1650,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K25" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L25" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M25" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N25" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O25" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="26">
@@ -1700,22 +1700,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K26" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L26" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M26" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N26" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O26" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="27">
@@ -1750,7 +1750,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K27" t="str">
-        <v>Error: expect(received).not.toMatch(expected) Expected pattern: not /ActionQueueDetails/ Received string: "http://customerportal.dev-ts.online/Ticket/ActionQueueDetails/1345"</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L27" t="str">
         <v>FAIL</v>
@@ -1759,13 +1759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N27" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O27" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="28">
@@ -1809,13 +1809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N28" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O28" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="29">
@@ -1850,22 +1850,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K29" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L29" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M29" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N29" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O29" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="30">
@@ -1909,13 +1909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N30" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O30" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="31">
@@ -1950,22 +1950,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K31" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L31" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M31" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N31" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O31" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="32">
@@ -2000,22 +2000,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K32" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L32" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M32" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N32" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O32" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="33">
@@ -2059,13 +2059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N33" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O33" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="34">
@@ -2109,13 +2109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N34" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O34" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="35">
@@ -2150,22 +2150,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K35" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L35" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M35" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N35" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O35" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="36">
@@ -2209,13 +2209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N36" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O36" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="37">
@@ -2259,13 +2259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N37" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O37" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="38">
@@ -2309,13 +2309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N38" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O38" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="39">
@@ -2359,13 +2359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N39" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O39" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="40">
@@ -2409,13 +2409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N40" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O40" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="41">
@@ -2459,13 +2459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N41" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O41" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="42">
@@ -2509,13 +2509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N42" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O42" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="43">
@@ -2559,13 +2559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N43" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O43" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="44">
@@ -2609,13 +2609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N44" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O44" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="45">
@@ -2659,13 +2659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N45" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O45" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="46">
@@ -2709,13 +2709,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N46" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O46" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="47">
@@ -2759,13 +2759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N47" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O47" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P47" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="48">
@@ -2809,13 +2809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N48" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O48" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P48" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="49">
@@ -2859,13 +2859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N49" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O49" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P49" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="50">
@@ -2909,13 +2909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N50" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O50" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="51">
@@ -2959,13 +2959,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N51" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O51" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="52">
@@ -3009,13 +3009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N52" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O52" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="53">
@@ -3059,13 +3059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N53" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O53" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="54">
@@ -3109,13 +3109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N54" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O54" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="55">
@@ -3159,13 +3159,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N55" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O55" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="56">
@@ -3209,13 +3209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N56" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O56" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P56" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="57">
@@ -3259,13 +3259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N57" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O57" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P57" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="58">
@@ -3309,13 +3309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N58" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O58" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P58" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="59">
@@ -3359,13 +3359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N59" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O59" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P59" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="60">
@@ -3409,13 +3409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N60" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O60" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P60" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="61">
@@ -3459,13 +3459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N61" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O61" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P61" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="62">
@@ -3509,13 +3509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N62" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O62" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="63">
@@ -3559,13 +3559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N63" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O63" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="64">
@@ -3609,13 +3609,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N64" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O64" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P64" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="65">
@@ -3659,13 +3659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N65" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O65" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P65" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="66">
@@ -3709,13 +3709,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N66" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O66" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P66" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="67">
@@ -3759,13 +3759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N67" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O67" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P67" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="68">
@@ -3809,13 +3809,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N68" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O68" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P68" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="69">
@@ -3859,13 +3859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N69" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O69" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P69" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="70">
@@ -3909,13 +3909,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N70" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O70" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P70" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="71">
@@ -3959,13 +3959,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N71" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O71" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P71" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="72">
@@ -4009,13 +4009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N72" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O72" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P72" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="73">
@@ -4059,13 +4059,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N73" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O73" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P73" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="74">
@@ -4109,13 +4109,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N74" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O74" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P74" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="75">
@@ -4159,13 +4159,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N75" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O75" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P75" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="76">
@@ -4209,13 +4209,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N76" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O76" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P76" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="77">
@@ -4259,13 +4259,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N77" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O77" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P77" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="78">
@@ -4309,13 +4309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N78" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O78" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P78" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="79">
@@ -4359,13 +4359,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N79" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O79" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P79" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="80">
@@ -4409,13 +4409,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N80" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O80" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P80" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="81">
@@ -4459,13 +4459,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N81" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O81" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P81" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="82" xml:space="preserve">
@@ -4516,13 +4516,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N82" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O82" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P82" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
@@ -4571,13 +4571,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N83" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O83" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P83" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="84" xml:space="preserve">
@@ -4624,13 +4624,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N84" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O84" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P84" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -4679,13 +4679,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N85" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O85" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P85" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -4732,13 +4732,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N86" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O86" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P86" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
@@ -4788,13 +4788,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N87" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O87" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P87" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="88" xml:space="preserve">
@@ -4842,13 +4842,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N88" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O88" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P88" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
@@ -4897,13 +4897,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N89" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O89" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P89" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -4951,13 +4951,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N90" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O90" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P90" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -5006,13 +5006,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N91" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O91" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P91" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
@@ -5061,13 +5061,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N92" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O92" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P92" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -5116,13 +5116,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N93" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O93" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P93" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -5171,13 +5171,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N94" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O94" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P94" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -5226,13 +5226,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N95" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O95" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P95" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -5281,13 +5281,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N96" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O96" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P96" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
@@ -5336,13 +5336,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N97" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O97" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P97" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="98" xml:space="preserve">
@@ -5393,13 +5393,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N98" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O98" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P98" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
@@ -5449,13 +5449,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N99" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O99" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P99" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
@@ -5505,13 +5505,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N100" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O100" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P100" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
@@ -5559,13 +5559,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N101" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O101" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P101" t="str">
-        <v>Regression run — 7/1/2026, 8:22:09 PM</v>
+        <v>Regression run — 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
   </sheetData>
@@ -5577,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P43"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5690,13 +5690,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N2" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O2" t="str">
         <v>Pass</v>
       </c>
       <c r="P2" t="str">
-        <v>Fixed — verified in Playwright regression 7/1/2026, 8:22:09 PM</v>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -5941,7 +5941,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K7" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L7" t="str">
         <v>Playwright Automation</v>
@@ -5950,13 +5950,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O7" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -6045,7 +6045,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K9" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L9" t="str">
         <v>Playwright Automation</v>
@@ -6054,13 +6054,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O9" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -6097,7 +6097,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K10" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L10" t="str">
         <v>Playwright Automation</v>
@@ -6106,13 +6106,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O10" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -6149,7 +6149,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K11" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L11" t="str">
         <v>Playwright Automation</v>
@@ -6158,13 +6158,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O11" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:56 PM</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -6791,9 +6791,1049 @@
         <v/>
       </c>
     </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>BUG-LOGIN-024</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Stat cards display all 4 metrics</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D24" t="str">
+        <v>TC-AQ-002</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-002
+3. Observe failure</v>
+      </c>
+      <c r="I24" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J24" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K24" t="str">
+        <v>New</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M24" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>BUG-LOGIN-025</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Grid displays all 10 expected column headers</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D25" t="str">
+        <v>TC-AQ-003</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-003
+3. Observe failure</v>
+      </c>
+      <c r="I25" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J25" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K25" t="str">
+        <v>New</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M25" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>BUG-LOGIN-027</v>
+      </c>
+      <c r="B26" t="str">
+        <v>No-match search shows empty grid</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D26" t="str">
+        <v>TC-AQ-020</v>
+      </c>
+      <c r="E26" t="str">
+        <v>High</v>
+      </c>
+      <c r="F26" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-020
+3. Observe failure</v>
+      </c>
+      <c r="I26" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J26" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K26" t="str">
+        <v>New</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M26" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>BUG-LOGIN-028</v>
+      </c>
+      <c r="B27" t="str">
+        <v>EXPORT button is visible and clickable</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D27" t="str">
+        <v>TC-AQ-014</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-014
+3. Observe failure</v>
+      </c>
+      <c r="I27" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J27" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K27" t="str">
+        <v>New</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M27" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>BUG-LOGIN-029</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Pagination shows correct format</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D28" t="str">
+        <v>TC-AQ-015</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-015
+3. Observe failure</v>
+      </c>
+      <c r="I28" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J28" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K28" t="str">
+        <v>New</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M28" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>BUG-LOGIN-030</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Perform Action opens ActionQueueDetails page</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D29" t="str">
+        <v>TC-AQ-004</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F29" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-004
+3. Observe failure</v>
+      </c>
+      <c r="I29" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J29" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K29" t="str">
+        <v>New</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M29" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>BUG-LOGIN-031</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Detail page displays all 5 information sections</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D30" t="str">
+        <v>TC-AQ-005</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-005
+3. Observe failure</v>
+      </c>
+      <c r="I30" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J30" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K30" t="str">
+        <v>New</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M30" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>BUG-LOGIN-032</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TIMELINE button opens timeline view</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D31" t="str">
+        <v>TC-AQ-026</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-026
+3. Observe failure</v>
+      </c>
+      <c r="I31" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J31" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K31" t="str">
+        <v>New</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M31" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>BUG-LOGIN-033</v>
+      </c>
+      <c r="B32" t="str">
+        <v>APPROVE dialog opens with correct elements</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D32" t="str">
+        <v>TC-AQ-006</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-006
+3. Observe failure</v>
+      </c>
+      <c r="I32" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J32" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K32" t="str">
+        <v>New</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M32" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>BUG-LOGIN-034</v>
+      </c>
+      <c r="B33" t="str">
+        <v>APPROVE with valid remarks submits successfully</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D33" t="str">
+        <v>TC-AQ-007</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-007
+3. Observe failure</v>
+      </c>
+      <c r="I33" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J33" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K33" t="str">
+        <v>New</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M33" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>BUG-LOGIN-035</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Cancel APPROVE dismisses without submitting</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D34" t="str">
+        <v>TC-AQ-010</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-010
+3. Observe failure</v>
+      </c>
+      <c r="I34" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J34" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K34" t="str">
+        <v>New</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M34" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>BUG-LOGIN-036</v>
+      </c>
+      <c r="B35" t="str">
+        <v>APPROVE empty remarks shows validation error</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D35" t="str">
+        <v>TC-AQ-016</v>
+      </c>
+      <c r="E35" t="str">
+        <v>High</v>
+      </c>
+      <c r="F35" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-016
+3. Observe failure</v>
+      </c>
+      <c r="I35" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J35" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K35" t="str">
+        <v>New</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M35" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>BUG-LOGIN-038</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Max length remarks (1000 chars) handled</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D36" t="str">
+        <v>TC-AQ-022</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F36" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-022
+3. Observe failure</v>
+      </c>
+      <c r="I36" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J36" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K36" t="str">
+        <v>New</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M36" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>BUG-LOGIN-039</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Whitespace-only remarks rejected</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D37" t="str">
+        <v>TC-AQ-023</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F37" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-023
+3. Observe failure</v>
+      </c>
+      <c r="I37" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J37" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K37" t="str">
+        <v>New</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M37" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>BUG-LOGIN-040</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SQL injection in remarks is sanitized</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D38" t="str">
+        <v>TC-AQ-024</v>
+      </c>
+      <c r="E38" t="str">
+        <v>High</v>
+      </c>
+      <c r="F38" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-024
+3. Observe failure</v>
+      </c>
+      <c r="I38" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J38" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K38" t="str">
+        <v>New</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M38" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>BUG-LOGIN-041</v>
+      </c>
+      <c r="B39" t="str">
+        <v>XSS payload in remarks @security</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D39" t="str">
+        <v>TC-AQ-025</v>
+      </c>
+      <c r="E39" t="str">
+        <v>High</v>
+      </c>
+      <c r="F39" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H39" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-025
+3. Observe failure</v>
+      </c>
+      <c r="I39" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J39" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K39" t="str">
+        <v>New</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M39" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>BUG-LOGIN-042</v>
+      </c>
+      <c r="B40" t="str">
+        <v>REOPEN dialog opens with correct elements</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D40" t="str">
+        <v>TC-AQ-008</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F40" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-008
+3. Observe failure</v>
+      </c>
+      <c r="I40" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J40" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K40" t="str">
+        <v>New</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M40" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>BUG-LOGIN-043</v>
+      </c>
+      <c r="B41" t="str">
+        <v>REOPEN with valid remarks submits successfully</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D41" t="str">
+        <v>TC-AQ-009</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-009
+3. Observe failure</v>
+      </c>
+      <c r="I41" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J41" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K41" t="str">
+        <v>New</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M41" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>BUG-LOGIN-044</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Cancel REOPEN dismisses without submitting</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D42" t="str">
+        <v>TC-AQ-011</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F42" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H42" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-011
+3. Observe failure</v>
+      </c>
+      <c r="I42" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J42" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K42" t="str">
+        <v>New</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M42" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>BUG-LOGIN-045</v>
+      </c>
+      <c r="B43" t="str">
+        <v>REOPEN empty remarks shows validation error</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D43" t="str">
+        <v>TC-AQ-017</v>
+      </c>
+      <c r="E43" t="str">
+        <v>High</v>
+      </c>
+      <c r="F43" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Login feature
+2. Execute: TC-AQ-017
+3. Observe failure</v>
+      </c>
+      <c r="I43" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J43" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K43" t="str">
+        <v>New</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M43" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P43"/>
   </ignoredErrors>
 </worksheet>
 </file>